--- a/2026年图册编制/2026年工程图册编制产品清单.xlsx
+++ b/2026年图册编制/2026年工程图册编制产品清单.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cmaj/Developer/雅洁五金2026年工程图册/2026年图册编制/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{BBE15268-8C01-0E49-BBFB-CB476380F3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="15960" windowHeight="16020"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34200" windowHeight="20200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$L$716</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5588,14 +5595,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5604,374 +5605,44 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -5994,331 +5665,42 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -6603,81 +5985,82 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L716"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.4615384615385" customWidth="1"/>
-    <col min="2" max="2" width="21.9519230769231" customWidth="1"/>
-    <col min="3" max="3" width="16.1826923076923" customWidth="1"/>
-    <col min="4" max="4" width="23.5480769230769" customWidth="1"/>
-    <col min="5" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="7" width="18.9038461538462" customWidth="1"/>
-    <col min="8" max="8" width="21.0288461538462" customWidth="1"/>
-    <col min="9" max="11" width="23.7788461538462" customWidth="1"/>
-    <col min="12" max="12" width="26.9230769230769" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="42.6640625" style="6" customWidth="1"/>
+    <col min="6" max="7" width="18.83203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="21" style="6" customWidth="1"/>
+    <col min="9" max="11" width="23.83203125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="27" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="88" customHeight="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" ht="88" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="38" customHeight="1" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="38" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="38" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="38" customHeight="1">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -6705,7 +6088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1" spans="1:12">
+    <row r="4" spans="1:12" ht="38" customHeight="1">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -6733,7 +6116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1" spans="1:12">
+    <row r="5" spans="1:12" ht="38" customHeight="1">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -6761,7 +6144,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1" spans="1:12">
+    <row r="6" spans="1:12" ht="38" customHeight="1">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -6789,7 +6172,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1" spans="1:12">
+    <row r="7" spans="1:12" ht="38" customHeight="1">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -6817,7 +6200,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1" spans="1:12">
+    <row r="8" spans="1:12" ht="38" customHeight="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -6845,7 +6228,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1" spans="1:12">
+    <row r="9" spans="1:12" ht="38" customHeight="1">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -6873,7 +6256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1" spans="1:12">
+    <row r="10" spans="1:12" ht="38" customHeight="1">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -6901,7 +6284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1" spans="1:12">
+    <row r="11" spans="1:12" ht="38" customHeight="1">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -6929,7 +6312,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1" spans="1:12">
+    <row r="12" spans="1:12" ht="38" customHeight="1">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -6957,7 +6340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1" spans="1:12">
+    <row r="13" spans="1:12" ht="38" customHeight="1">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -6985,7 +6368,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1" spans="1:12">
+    <row r="14" spans="1:12" ht="38" customHeight="1">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -7013,7 +6396,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1" spans="1:12">
+    <row r="15" spans="1:12" ht="38" customHeight="1">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -7041,7 +6424,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" ht="38" customHeight="1" spans="1:12">
+    <row r="16" spans="1:12" ht="38" customHeight="1">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -7069,7 +6452,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1" spans="1:12">
+    <row r="17" spans="1:12" ht="38" customHeight="1">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -7097,7 +6480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1" spans="1:12">
+    <row r="18" spans="1:12" ht="38" customHeight="1">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -7125,7 +6508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1" spans="1:12">
+    <row r="19" spans="1:12" ht="38" customHeight="1">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -7153,7 +6536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" ht="38" customHeight="1" spans="1:12">
+    <row r="20" spans="1:12" ht="38" customHeight="1">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -7181,7 +6564,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" ht="38" customHeight="1" spans="1:12">
+    <row r="21" spans="1:12" ht="38" customHeight="1">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -7209,7 +6592,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" ht="38" customHeight="1" spans="1:12">
+    <row r="22" spans="1:12" ht="38" customHeight="1">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -7237,7 +6620,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1" spans="1:12">
+    <row r="23" spans="1:12" ht="38" customHeight="1">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -7265,7 +6648,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" ht="38" customHeight="1" spans="1:12">
+    <row r="24" spans="1:12" ht="38" customHeight="1">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -7293,7 +6676,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" ht="38" customHeight="1" spans="1:12">
+    <row r="25" spans="1:12" ht="38" customHeight="1">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -7321,7 +6704,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" ht="38" customHeight="1" spans="1:12">
+    <row r="26" spans="1:12" ht="38" customHeight="1">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -7349,7 +6732,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" ht="38" customHeight="1" spans="1:12">
+    <row r="27" spans="1:12" ht="38" customHeight="1">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -7377,7 +6760,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1" spans="1:12">
+    <row r="28" spans="1:12" ht="38" customHeight="1">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -7405,7 +6788,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" ht="38" customHeight="1" spans="1:12">
+    <row r="29" spans="1:12" ht="38" customHeight="1">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -7433,7 +6816,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1" spans="1:12">
+    <row r="30" spans="1:12" ht="38" customHeight="1">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -7461,7 +6844,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" ht="38" customHeight="1" spans="1:12">
+    <row r="31" spans="1:12" ht="38" customHeight="1">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -7489,7 +6872,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1" spans="1:12">
+    <row r="32" spans="1:12" ht="38" customHeight="1">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -7517,7 +6900,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1" spans="1:12">
+    <row r="33" spans="1:12" ht="38" customHeight="1">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -7545,7 +6928,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1" spans="1:12">
+    <row r="34" spans="1:12" ht="38" customHeight="1">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -7573,7 +6956,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" ht="38" customHeight="1" spans="1:12">
+    <row r="35" spans="1:12" ht="38" customHeight="1">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -7601,7 +6984,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1" spans="1:12">
+    <row r="36" spans="1:12" ht="38" customHeight="1">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -7629,7 +7012,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1" spans="1:12">
+    <row r="37" spans="1:12" ht="38" customHeight="1">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -7657,7 +7040,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" ht="38" customHeight="1" spans="1:12">
+    <row r="38" spans="1:12" ht="38" customHeight="1">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -7685,7 +7068,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" ht="38" customHeight="1" spans="1:12">
+    <row r="39" spans="1:12" ht="38" customHeight="1">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -7705,7 +7088,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" ht="38" customHeight="1" spans="1:12">
+    <row r="40" spans="1:12" ht="38" customHeight="1">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -7733,7 +7116,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" ht="38" customHeight="1" spans="1:12">
+    <row r="41" spans="1:12" ht="38" customHeight="1">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -7761,7 +7144,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" ht="38" customHeight="1" spans="1:12">
+    <row r="42" spans="1:12" ht="38" customHeight="1">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -7789,7 +7172,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1" spans="1:12">
+    <row r="43" spans="1:12" ht="38" customHeight="1">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -7817,7 +7200,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" ht="38" customHeight="1" spans="1:12">
+    <row r="44" spans="1:12" ht="38" customHeight="1">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -7845,7 +7228,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1" spans="1:12">
+    <row r="45" spans="1:12" ht="38" customHeight="1">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -7873,7 +7256,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" ht="38" customHeight="1" spans="1:12">
+    <row r="46" spans="1:12" ht="38" customHeight="1">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -7901,7 +7284,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="47" ht="38" customHeight="1" spans="1:12">
+    <row r="47" spans="1:12" ht="38" customHeight="1">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -7929,7 +7312,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" ht="38" customHeight="1" spans="1:12">
+    <row r="48" spans="1:12" ht="38" customHeight="1">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -7957,7 +7340,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49" ht="38" customHeight="1" spans="1:12">
+    <row r="49" spans="1:12" ht="38" customHeight="1">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -7985,7 +7368,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" ht="38" customHeight="1" spans="1:12">
+    <row r="50" spans="1:12" ht="38" customHeight="1">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -8013,7 +7396,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" ht="38" customHeight="1" spans="1:12">
+    <row r="51" spans="1:12" ht="38" customHeight="1">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -8041,7 +7424,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" ht="38" customHeight="1" spans="1:12">
+    <row r="52" spans="1:12" ht="38" customHeight="1">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -8069,7 +7452,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" ht="38" customHeight="1" spans="1:12">
+    <row r="53" spans="1:12" ht="38" customHeight="1">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -8097,7 +7480,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" ht="38" customHeight="1" spans="1:12">
+    <row r="54" spans="1:12" ht="38" customHeight="1">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -8125,7 +7508,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" ht="38" customHeight="1" spans="1:12">
+    <row r="55" spans="1:12" ht="38" customHeight="1">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -8153,7 +7536,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="56" ht="38" customHeight="1" spans="1:12">
+    <row r="56" spans="1:12" ht="38" customHeight="1">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -8181,7 +7564,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" ht="38" customHeight="1" spans="1:12">
+    <row r="57" spans="1:12" ht="38" customHeight="1">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -8203,7 +7586,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" ht="38" customHeight="1" spans="1:12">
+    <row r="58" spans="1:12" ht="38" customHeight="1">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -8231,7 +7614,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" ht="38" customHeight="1" spans="1:12">
+    <row r="59" spans="1:12" ht="38" customHeight="1">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -8259,7 +7642,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="60" ht="38" customHeight="1" spans="1:12">
+    <row r="60" spans="1:12" ht="38" customHeight="1">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -8287,7 +7670,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" ht="38" customHeight="1" spans="1:12">
+    <row r="61" spans="1:12" ht="38" customHeight="1">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -8315,7 +7698,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="62" ht="38" customHeight="1" spans="1:12">
+    <row r="62" spans="1:12" ht="38" customHeight="1">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -8343,7 +7726,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" ht="38" customHeight="1" spans="1:12">
+    <row r="63" spans="1:12" ht="38" customHeight="1">
       <c r="A63" s="4">
         <v>61</v>
       </c>
@@ -8371,7 +7754,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" ht="38" customHeight="1" spans="1:12">
+    <row r="64" spans="1:12" ht="38" customHeight="1">
       <c r="A64" s="4">
         <v>62</v>
       </c>
@@ -8399,7 +7782,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="65" ht="38" customHeight="1" spans="1:12">
+    <row r="65" spans="1:12" ht="38" customHeight="1">
       <c r="A65" s="4">
         <v>63</v>
       </c>
@@ -8427,7 +7810,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" ht="38" customHeight="1" spans="1:12">
+    <row r="66" spans="1:12" ht="38" customHeight="1">
       <c r="A66" s="4">
         <v>64</v>
       </c>
@@ -8455,7 +7838,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" ht="38" customHeight="1" spans="1:12">
+    <row r="67" spans="1:12" ht="38" customHeight="1">
       <c r="A67" s="4">
         <v>65</v>
       </c>
@@ -8483,7 +7866,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="68" ht="38" customHeight="1" spans="1:12">
+    <row r="68" spans="1:12" ht="38" customHeight="1">
       <c r="A68" s="4">
         <v>66</v>
       </c>
@@ -8511,7 +7894,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="69" ht="38" customHeight="1" spans="1:12">
+    <row r="69" spans="1:12" ht="38" customHeight="1">
       <c r="A69" s="4">
         <v>67</v>
       </c>
@@ -8539,7 +7922,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="70" ht="38" customHeight="1" spans="1:12">
+    <row r="70" spans="1:12" ht="38" customHeight="1">
       <c r="A70" s="4">
         <v>68</v>
       </c>
@@ -8567,7 +7950,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" ht="38" customHeight="1" spans="1:12">
+    <row r="71" spans="1:12" ht="38" customHeight="1">
       <c r="A71" s="4">
         <v>69</v>
       </c>
@@ -8595,7 +7978,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="72" ht="38" customHeight="1" spans="1:12">
+    <row r="72" spans="1:12" ht="38" customHeight="1">
       <c r="A72" s="4">
         <v>70</v>
       </c>
@@ -8623,7 +8006,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" ht="38" customHeight="1" spans="1:12">
+    <row r="73" spans="1:12" ht="38" customHeight="1">
       <c r="A73" s="4">
         <v>71</v>
       </c>
@@ -8651,7 +8034,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="74" ht="38" customHeight="1" spans="1:12">
+    <row r="74" spans="1:12" ht="38" customHeight="1">
       <c r="A74" s="4">
         <v>72</v>
       </c>
@@ -8679,7 +8062,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" ht="38" customHeight="1" spans="1:12">
+    <row r="75" spans="1:12" ht="38" customHeight="1">
       <c r="A75" s="4">
         <v>73</v>
       </c>
@@ -8707,7 +8090,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="76" ht="38" customHeight="1" spans="1:12">
+    <row r="76" spans="1:12" ht="38" customHeight="1">
       <c r="A76" s="4">
         <v>74</v>
       </c>
@@ -8735,7 +8118,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="77" ht="38" customHeight="1" spans="1:12">
+    <row r="77" spans="1:12" ht="38" customHeight="1">
       <c r="A77" s="4">
         <v>75</v>
       </c>
@@ -8763,7 +8146,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="78" ht="38" customHeight="1" spans="1:12">
+    <row r="78" spans="1:12" ht="38" customHeight="1">
       <c r="A78" s="4">
         <v>76</v>
       </c>
@@ -8791,7 +8174,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="79" ht="38" customHeight="1" spans="1:12">
+    <row r="79" spans="1:12" ht="38" customHeight="1">
       <c r="A79" s="4">
         <v>77</v>
       </c>
@@ -8819,7 +8202,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" ht="38" customHeight="1" spans="1:12">
+    <row r="80" spans="1:12" ht="38" customHeight="1">
       <c r="A80" s="4">
         <v>78</v>
       </c>
@@ -8847,7 +8230,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="81" ht="38" customHeight="1" spans="1:12">
+    <row r="81" spans="1:12" ht="38" customHeight="1">
       <c r="A81" s="4">
         <v>79</v>
       </c>
@@ -8875,7 +8258,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="82" ht="38" customHeight="1" spans="1:12">
+    <row r="82" spans="1:12" ht="38" customHeight="1">
       <c r="A82" s="4">
         <v>80</v>
       </c>
@@ -8903,7 +8286,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="83" ht="38" customHeight="1" spans="1:12">
+    <row r="83" spans="1:12" ht="38" customHeight="1">
       <c r="A83" s="4">
         <v>81</v>
       </c>
@@ -8931,7 +8314,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="84" ht="38" customHeight="1" spans="1:12">
+    <row r="84" spans="1:12" ht="38" customHeight="1">
       <c r="A84" s="4">
         <v>82</v>
       </c>
@@ -8959,7 +8342,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" ht="38" customHeight="1" spans="1:12">
+    <row r="85" spans="1:12" ht="38" customHeight="1">
       <c r="A85" s="4">
         <v>83</v>
       </c>
@@ -8987,7 +8370,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="86" ht="38" customHeight="1" spans="1:12">
+    <row r="86" spans="1:12" ht="38" customHeight="1">
       <c r="A86" s="4">
         <v>84</v>
       </c>
@@ -9015,7 +8398,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="87" ht="38" customHeight="1" spans="1:12">
+    <row r="87" spans="1:12" ht="38" customHeight="1">
       <c r="A87" s="4">
         <v>85</v>
       </c>
@@ -9043,7 +8426,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="88" ht="38" customHeight="1" spans="1:12">
+    <row r="88" spans="1:12" ht="38" customHeight="1">
       <c r="A88" s="4">
         <v>86</v>
       </c>
@@ -9071,7 +8454,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="89" ht="38" customHeight="1" spans="1:12">
+    <row r="89" spans="1:12" ht="38" customHeight="1">
       <c r="A89" s="4">
         <v>87</v>
       </c>
@@ -9099,7 +8482,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="90" ht="38" customHeight="1" spans="1:12">
+    <row r="90" spans="1:12" ht="38" customHeight="1">
       <c r="A90" s="4">
         <v>88</v>
       </c>
@@ -9127,7 +8510,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="91" ht="38" customHeight="1" spans="1:12">
+    <row r="91" spans="1:12" ht="38" customHeight="1">
       <c r="A91" s="4">
         <v>89</v>
       </c>
@@ -9155,7 +8538,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="92" ht="38" customHeight="1" spans="1:12">
+    <row r="92" spans="1:12" ht="38" customHeight="1">
       <c r="A92" s="4">
         <v>90</v>
       </c>
@@ -9183,7 +8566,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" ht="38" customHeight="1" spans="1:12">
+    <row r="93" spans="1:12" ht="38" customHeight="1">
       <c r="A93" s="4">
         <v>91</v>
       </c>
@@ -9211,7 +8594,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="94" ht="38" customHeight="1" spans="1:12">
+    <row r="94" spans="1:12" ht="38" customHeight="1">
       <c r="A94" s="4">
         <v>92</v>
       </c>
@@ -9239,7 +8622,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="95" ht="38" customHeight="1" spans="1:12">
+    <row r="95" spans="1:12" ht="38" customHeight="1">
       <c r="A95" s="4">
         <v>93</v>
       </c>
@@ -9267,7 +8650,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="96" ht="38" customHeight="1" spans="1:12">
+    <row r="96" spans="1:12" ht="38" customHeight="1">
       <c r="A96" s="4">
         <v>94</v>
       </c>
@@ -9295,7 +8678,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="97" ht="38" customHeight="1" spans="1:12">
+    <row r="97" spans="1:12" ht="38" customHeight="1">
       <c r="A97" s="4">
         <v>95</v>
       </c>
@@ -9323,7 +8706,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="98" ht="38" customHeight="1" spans="1:12">
+    <row r="98" spans="1:12" ht="38" customHeight="1">
       <c r="A98" s="4">
         <v>96</v>
       </c>
@@ -9351,7 +8734,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" ht="38" customHeight="1" spans="1:12">
+    <row r="99" spans="1:12" ht="38" customHeight="1">
       <c r="A99" s="4">
         <v>97</v>
       </c>
@@ -9379,7 +8762,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="100" ht="38" customHeight="1" spans="1:12">
+    <row r="100" spans="1:12" ht="38" customHeight="1">
       <c r="A100" s="4">
         <v>98</v>
       </c>
@@ -9407,7 +8790,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="101" ht="38" customHeight="1" spans="1:12">
+    <row r="101" spans="1:12" ht="38" customHeight="1">
       <c r="A101" s="4">
         <v>99</v>
       </c>
@@ -9435,7 +8818,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="102" ht="38" customHeight="1" spans="1:12">
+    <row r="102" spans="1:12" ht="38" customHeight="1">
       <c r="A102" s="4">
         <v>100</v>
       </c>
@@ -9463,7 +8846,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="103" ht="38" customHeight="1" spans="1:12">
+    <row r="103" spans="1:12" ht="38" customHeight="1">
       <c r="A103" s="4">
         <v>101</v>
       </c>
@@ -9491,7 +8874,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="104" ht="38" customHeight="1" spans="1:12">
+    <row r="104" spans="1:12" ht="38" customHeight="1">
       <c r="A104" s="4">
         <v>102</v>
       </c>
@@ -9519,7 +8902,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="105" ht="38" customHeight="1" spans="1:12">
+    <row r="105" spans="1:12" ht="38" customHeight="1">
       <c r="A105" s="4">
         <v>103</v>
       </c>
@@ -9547,7 +8930,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="106" ht="38" customHeight="1" spans="1:12">
+    <row r="106" spans="1:12" ht="38" customHeight="1">
       <c r="A106" s="4">
         <v>104</v>
       </c>
@@ -9575,7 +8958,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="107" ht="38" customHeight="1" spans="1:12">
+    <row r="107" spans="1:12" ht="38" customHeight="1">
       <c r="A107" s="4">
         <v>105</v>
       </c>
@@ -9603,7 +8986,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="108" ht="38" customHeight="1" spans="1:12">
+    <row r="108" spans="1:12" ht="38" customHeight="1">
       <c r="A108" s="4">
         <v>106</v>
       </c>
@@ -9631,7 +9014,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="109" ht="38" customHeight="1" spans="1:12">
+    <row r="109" spans="1:12" ht="38" customHeight="1">
       <c r="A109" s="4">
         <v>107</v>
       </c>
@@ -9659,7 +9042,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="110" ht="38" customHeight="1" spans="1:12">
+    <row r="110" spans="1:12" ht="38" customHeight="1">
       <c r="A110" s="4">
         <v>108</v>
       </c>
@@ -9687,7 +9070,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="111" ht="38" customHeight="1" spans="1:12">
+    <row r="111" spans="1:12" ht="38" customHeight="1">
       <c r="A111" s="4">
         <v>109</v>
       </c>
@@ -9715,7 +9098,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="112" ht="38" customHeight="1" spans="1:12">
+    <row r="112" spans="1:12" ht="38" customHeight="1">
       <c r="A112" s="4">
         <v>110</v>
       </c>
@@ -9743,7 +9126,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="113" ht="38" customHeight="1" spans="1:12">
+    <row r="113" spans="1:12" ht="38" customHeight="1">
       <c r="A113" s="4">
         <v>111</v>
       </c>
@@ -9771,7 +9154,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="114" ht="38" customHeight="1" spans="1:12">
+    <row r="114" spans="1:12" ht="38" customHeight="1">
       <c r="A114" s="4">
         <v>112</v>
       </c>
@@ -9799,7 +9182,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="115" ht="38" customHeight="1" spans="1:12">
+    <row r="115" spans="1:12" ht="38" customHeight="1">
       <c r="A115" s="4">
         <v>113</v>
       </c>
@@ -9827,7 +9210,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="116" ht="38" customHeight="1" spans="1:12">
+    <row r="116" spans="1:12" ht="38" customHeight="1">
       <c r="A116" s="4">
         <v>114</v>
       </c>
@@ -9855,7 +9238,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="117" ht="38" customHeight="1" spans="1:12">
+    <row r="117" spans="1:12" ht="38" customHeight="1">
       <c r="A117" s="4">
         <v>115</v>
       </c>
@@ -9883,7 +9266,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="118" ht="38" customHeight="1" spans="1:12">
+    <row r="118" spans="1:12" ht="38" customHeight="1">
       <c r="A118" s="4">
         <v>116</v>
       </c>
@@ -9911,7 +9294,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="119" ht="38" customHeight="1" spans="1:12">
+    <row r="119" spans="1:12" ht="38" customHeight="1">
       <c r="A119" s="4">
         <v>117</v>
       </c>
@@ -9939,7 +9322,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="120" ht="38" customHeight="1" spans="1:12">
+    <row r="120" spans="1:12" ht="38" customHeight="1">
       <c r="A120" s="4">
         <v>118</v>
       </c>
@@ -9967,7 +9350,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="121" ht="38" customHeight="1" spans="1:12">
+    <row r="121" spans="1:12" ht="38" customHeight="1">
       <c r="A121" s="4">
         <v>119</v>
       </c>
@@ -9995,7 +9378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="122" ht="38" customHeight="1" spans="1:12">
+    <row r="122" spans="1:12" ht="38" customHeight="1">
       <c r="A122" s="4">
         <v>120</v>
       </c>
@@ -10023,7 +9406,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="123" ht="38" customHeight="1" spans="1:12">
+    <row r="123" spans="1:12" ht="38" customHeight="1">
       <c r="A123" s="4">
         <v>121</v>
       </c>
@@ -10051,7 +9434,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="124" ht="38" customHeight="1" spans="1:12">
+    <row r="124" spans="1:12" ht="38" customHeight="1">
       <c r="A124" s="4">
         <v>122</v>
       </c>
@@ -10079,7 +9462,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="125" ht="38" customHeight="1" spans="1:12">
+    <row r="125" spans="1:12" ht="38" customHeight="1">
       <c r="A125" s="4">
         <v>123</v>
       </c>
@@ -10107,7 +9490,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="126" ht="38" customHeight="1" spans="1:12">
+    <row r="126" spans="1:12" ht="38" customHeight="1">
       <c r="A126" s="4">
         <v>124</v>
       </c>
@@ -10135,7 +9518,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="127" ht="38" customHeight="1" spans="1:12">
+    <row r="127" spans="1:12" ht="38" customHeight="1">
       <c r="A127" s="4">
         <v>125</v>
       </c>
@@ -10163,7 +9546,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="128" ht="38" customHeight="1" spans="1:12">
+    <row r="128" spans="1:12" ht="38" customHeight="1">
       <c r="A128" s="4">
         <v>126</v>
       </c>
@@ -10191,7 +9574,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="129" ht="38" customHeight="1" spans="1:12">
+    <row r="129" spans="1:12" ht="38" customHeight="1">
       <c r="A129" s="4">
         <v>127</v>
       </c>
@@ -10219,7 +9602,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="130" ht="38" customHeight="1" spans="1:12">
+    <row r="130" spans="1:12" ht="38" customHeight="1">
       <c r="A130" s="4">
         <v>128</v>
       </c>
@@ -10247,7 +9630,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" ht="38" customHeight="1" spans="1:12">
+    <row r="131" spans="1:12" ht="38" customHeight="1">
       <c r="A131" s="4">
         <v>129</v>
       </c>
@@ -10275,7 +9658,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="132" ht="38" customHeight="1" spans="1:12">
+    <row r="132" spans="1:12" ht="38" customHeight="1">
       <c r="A132" s="4">
         <v>130</v>
       </c>
@@ -10303,7 +9686,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="133" ht="38" customHeight="1" spans="1:12">
+    <row r="133" spans="1:12" ht="38" customHeight="1">
       <c r="A133" s="4">
         <v>131</v>
       </c>
@@ -10331,7 +9714,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="134" ht="38" customHeight="1" spans="1:12">
+    <row r="134" spans="1:12" ht="38" customHeight="1">
       <c r="A134" s="4">
         <v>132</v>
       </c>
@@ -10359,7 +9742,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="135" ht="38" customHeight="1" spans="1:12">
+    <row r="135" spans="1:12" ht="38" customHeight="1">
       <c r="A135" s="4">
         <v>133</v>
       </c>
@@ -10387,7 +9770,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="136" ht="38" customHeight="1" spans="1:12">
+    <row r="136" spans="1:12" ht="38" customHeight="1">
       <c r="A136" s="4">
         <v>134</v>
       </c>
@@ -10415,7 +9798,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="137" ht="38" customHeight="1" spans="1:12">
+    <row r="137" spans="1:12" ht="38" customHeight="1">
       <c r="A137" s="4">
         <v>135</v>
       </c>
@@ -10443,7 +9826,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="138" ht="38" customHeight="1" spans="1:12">
+    <row r="138" spans="1:12" ht="38" customHeight="1">
       <c r="A138" s="4">
         <v>136</v>
       </c>
@@ -10471,7 +9854,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="38" customHeight="1" spans="1:12">
+    <row r="139" spans="1:12" ht="38" customHeight="1">
       <c r="A139" s="4">
         <v>137</v>
       </c>
@@ -10499,7 +9882,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" ht="38" customHeight="1" spans="1:12">
+    <row r="140" spans="1:12" ht="38" customHeight="1">
       <c r="A140" s="4">
         <v>138</v>
       </c>
@@ -10527,7 +9910,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="141" ht="38" customHeight="1" spans="1:12">
+    <row r="141" spans="1:12" ht="38" customHeight="1">
       <c r="A141" s="4">
         <v>139</v>
       </c>
@@ -10555,7 +9938,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="142" ht="38" customHeight="1" spans="1:12">
+    <row r="142" spans="1:12" ht="38" customHeight="1">
       <c r="A142" s="4">
         <v>140</v>
       </c>
@@ -10583,7 +9966,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="143" ht="38" customHeight="1" spans="1:12">
+    <row r="143" spans="1:12" ht="38" customHeight="1">
       <c r="A143" s="4">
         <v>141</v>
       </c>
@@ -10611,7 +9994,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="144" ht="38" customHeight="1" spans="1:12">
+    <row r="144" spans="1:12" ht="38" customHeight="1">
       <c r="A144" s="4">
         <v>142</v>
       </c>
@@ -10639,7 +10022,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="145" ht="38" customHeight="1" spans="1:12">
+    <row r="145" spans="1:12" ht="38" customHeight="1">
       <c r="A145" s="4">
         <v>143</v>
       </c>
@@ -10667,7 +10050,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="146" ht="38" customHeight="1" spans="1:12">
+    <row r="146" spans="1:12" ht="38" customHeight="1">
       <c r="A146" s="4">
         <v>144</v>
       </c>
@@ -10695,7 +10078,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="147" ht="38" customHeight="1" spans="1:12">
+    <row r="147" spans="1:12" ht="38" customHeight="1">
       <c r="A147" s="4">
         <v>145</v>
       </c>
@@ -10723,7 +10106,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="148" ht="38" customHeight="1" spans="1:12">
+    <row r="148" spans="1:12" ht="38" customHeight="1">
       <c r="A148" s="4">
         <v>146</v>
       </c>
@@ -10751,7 +10134,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="149" ht="38" customHeight="1" spans="1:12">
+    <row r="149" spans="1:12" ht="38" customHeight="1">
       <c r="A149" s="4">
         <v>147</v>
       </c>
@@ -10779,7 +10162,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="150" ht="38" customHeight="1" spans="1:12">
+    <row r="150" spans="1:12" ht="38" customHeight="1">
       <c r="A150" s="4">
         <v>148</v>
       </c>
@@ -10807,7 +10190,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="151" ht="38" customHeight="1" spans="1:12">
+    <row r="151" spans="1:12" ht="38" customHeight="1">
       <c r="A151" s="4">
         <v>149</v>
       </c>
@@ -10835,7 +10218,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="152" ht="38" customHeight="1" spans="1:12">
+    <row r="152" spans="1:12" ht="38" customHeight="1">
       <c r="A152" s="4">
         <v>150</v>
       </c>
@@ -10863,7 +10246,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="153" ht="38" customHeight="1" spans="1:12">
+    <row r="153" spans="1:12" ht="38" customHeight="1">
       <c r="A153" s="4">
         <v>151</v>
       </c>
@@ -10891,7 +10274,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="154" ht="38" customHeight="1" spans="1:12">
+    <row r="154" spans="1:12" ht="38" customHeight="1">
       <c r="A154" s="4">
         <v>152</v>
       </c>
@@ -10919,7 +10302,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="155" ht="38" customHeight="1" spans="1:12">
+    <row r="155" spans="1:12" ht="38" customHeight="1">
       <c r="A155" s="4">
         <v>153</v>
       </c>
@@ -10947,7 +10330,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="156" ht="38" customHeight="1" spans="1:12">
+    <row r="156" spans="1:12" ht="38" customHeight="1">
       <c r="A156" s="4">
         <v>154</v>
       </c>
@@ -10975,7 +10358,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="157" ht="38" customHeight="1" spans="1:12">
+    <row r="157" spans="1:12" ht="38" customHeight="1">
       <c r="A157" s="4">
         <v>155</v>
       </c>
@@ -11003,7 +10386,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="158" ht="38" customHeight="1" spans="1:12">
+    <row r="158" spans="1:12" ht="38" customHeight="1">
       <c r="A158" s="4">
         <v>156</v>
       </c>
@@ -11031,7 +10414,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="159" ht="38" customHeight="1" spans="1:12">
+    <row r="159" spans="1:12" ht="38" customHeight="1">
       <c r="A159" s="4">
         <v>157</v>
       </c>
@@ -11059,7 +10442,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="160" ht="38" customHeight="1" spans="1:12">
+    <row r="160" spans="1:12" ht="38" customHeight="1">
       <c r="A160" s="4">
         <v>158</v>
       </c>
@@ -11087,7 +10470,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="161" ht="38" customHeight="1" spans="1:12">
+    <row r="161" spans="1:12" ht="38" customHeight="1">
       <c r="A161" s="4">
         <v>159</v>
       </c>
@@ -11115,7 +10498,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="162" ht="38" customHeight="1" spans="1:12">
+    <row r="162" spans="1:12" ht="38" customHeight="1">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -11143,7 +10526,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="163" ht="38" customHeight="1" spans="1:12">
+    <row r="163" spans="1:12" ht="38" customHeight="1">
       <c r="A163" s="4">
         <v>161</v>
       </c>
@@ -11171,7 +10554,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="164" ht="38" customHeight="1" spans="1:12">
+    <row r="164" spans="1:12" ht="38" customHeight="1">
       <c r="A164" s="4">
         <v>162</v>
       </c>
@@ -11199,7 +10582,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="165" ht="38" customHeight="1" spans="1:12">
+    <row r="165" spans="1:12" ht="38" customHeight="1">
       <c r="A165" s="4">
         <v>163</v>
       </c>
@@ -11227,7 +10610,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="166" ht="38" customHeight="1" spans="1:12">
+    <row r="166" spans="1:12" ht="38" customHeight="1">
       <c r="A166" s="4">
         <v>164</v>
       </c>
@@ -11255,7 +10638,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="167" ht="38" customHeight="1" spans="1:12">
+    <row r="167" spans="1:12" ht="38" customHeight="1">
       <c r="A167" s="4">
         <v>165</v>
       </c>
@@ -11283,7 +10666,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="168" ht="38" customHeight="1" spans="1:12">
+    <row r="168" spans="1:12" ht="38" customHeight="1">
       <c r="A168" s="4">
         <v>166</v>
       </c>
@@ -11311,7 +10694,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="169" ht="38" customHeight="1" spans="1:12">
+    <row r="169" spans="1:12" ht="38" customHeight="1">
       <c r="A169" s="4">
         <v>167</v>
       </c>
@@ -11339,7 +10722,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="170" ht="38" customHeight="1" spans="1:12">
+    <row r="170" spans="1:12" ht="38" customHeight="1">
       <c r="A170" s="4">
         <v>168</v>
       </c>
@@ -11367,7 +10750,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="171" ht="38" customHeight="1" spans="1:12">
+    <row r="171" spans="1:12" ht="38" customHeight="1">
       <c r="A171" s="4">
         <v>169</v>
       </c>
@@ -11395,7 +10778,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="172" ht="38" customHeight="1" spans="1:12">
+    <row r="172" spans="1:12" ht="38" customHeight="1">
       <c r="A172" s="4">
         <v>170</v>
       </c>
@@ -11423,7 +10806,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="173" ht="38" customHeight="1" spans="1:12">
+    <row r="173" spans="1:12" ht="38" customHeight="1">
       <c r="A173" s="4">
         <v>171</v>
       </c>
@@ -11451,7 +10834,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="174" ht="38" customHeight="1" spans="1:12">
+    <row r="174" spans="1:12" ht="38" customHeight="1">
       <c r="A174" s="4">
         <v>172</v>
       </c>
@@ -11479,7 +10862,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="175" ht="38" customHeight="1" spans="1:12">
+    <row r="175" spans="1:12" ht="38" customHeight="1">
       <c r="A175" s="4">
         <v>173</v>
       </c>
@@ -11507,7 +10890,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="176" ht="38" customHeight="1" spans="1:12">
+    <row r="176" spans="1:12" ht="38" customHeight="1">
       <c r="A176" s="4">
         <v>174</v>
       </c>
@@ -11535,7 +10918,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177" ht="38" customHeight="1" spans="1:12">
+    <row r="177" spans="1:12" ht="38" customHeight="1">
       <c r="A177" s="4">
         <v>175</v>
       </c>
@@ -11563,7 +10946,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="178" ht="38" customHeight="1" spans="1:12">
+    <row r="178" spans="1:12" ht="38" customHeight="1">
       <c r="A178" s="4">
         <v>176</v>
       </c>
@@ -11591,7 +10974,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="179" ht="38" customHeight="1" spans="1:12">
+    <row r="179" spans="1:12" ht="38" customHeight="1">
       <c r="A179" s="4">
         <v>177</v>
       </c>
@@ -11619,7 +11002,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="180" ht="38" customHeight="1" spans="1:12">
+    <row r="180" spans="1:12" ht="38" customHeight="1">
       <c r="A180" s="4">
         <v>178</v>
       </c>
@@ -11647,7 +11030,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="181" ht="38" customHeight="1" spans="1:12">
+    <row r="181" spans="1:12" ht="38" customHeight="1">
       <c r="A181" s="4">
         <v>179</v>
       </c>
@@ -11675,7 +11058,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="182" ht="38" customHeight="1" spans="1:12">
+    <row r="182" spans="1:12" ht="38" customHeight="1">
       <c r="A182" s="4">
         <v>180</v>
       </c>
@@ -11703,7 +11086,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="183" ht="38" customHeight="1" spans="1:12">
+    <row r="183" spans="1:12" ht="38" customHeight="1">
       <c r="A183" s="4">
         <v>181</v>
       </c>
@@ -11731,7 +11114,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="184" ht="38" customHeight="1" spans="1:12">
+    <row r="184" spans="1:12" ht="38" customHeight="1">
       <c r="A184" s="4">
         <v>182</v>
       </c>
@@ -11759,7 +11142,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="185" ht="38" customHeight="1" spans="1:12">
+    <row r="185" spans="1:12" ht="38" customHeight="1">
       <c r="A185" s="4">
         <v>183</v>
       </c>
@@ -11787,7 +11170,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="186" ht="38" customHeight="1" spans="1:12">
+    <row r="186" spans="1:12" ht="38" customHeight="1">
       <c r="A186" s="4">
         <v>184</v>
       </c>
@@ -11815,7 +11198,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="187" ht="38" customHeight="1" spans="1:12">
+    <row r="187" spans="1:12" ht="38" customHeight="1">
       <c r="A187" s="4">
         <v>185</v>
       </c>
@@ -11843,7 +11226,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="188" ht="38" customHeight="1" spans="1:12">
+    <row r="188" spans="1:12" ht="38" customHeight="1">
       <c r="A188" s="4">
         <v>186</v>
       </c>
@@ -11871,7 +11254,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="189" ht="38" customHeight="1" spans="1:12">
+    <row r="189" spans="1:12" ht="38" customHeight="1">
       <c r="A189" s="4">
         <v>187</v>
       </c>
@@ -11899,7 +11282,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="190" ht="38" customHeight="1" spans="1:12">
+    <row r="190" spans="1:12" ht="38" customHeight="1">
       <c r="A190" s="4">
         <v>188</v>
       </c>
@@ -11927,7 +11310,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="191" ht="38" customHeight="1" spans="1:12">
+    <row r="191" spans="1:12" ht="38" customHeight="1">
       <c r="A191" s="4">
         <v>189</v>
       </c>
@@ -11955,7 +11338,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="192" ht="38" customHeight="1" spans="1:12">
+    <row r="192" spans="1:12" ht="38" customHeight="1">
       <c r="A192" s="4">
         <v>190</v>
       </c>
@@ -11983,7 +11366,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="193" ht="38" customHeight="1" spans="1:12">
+    <row r="193" spans="1:12" ht="38" customHeight="1">
       <c r="A193" s="4">
         <v>191</v>
       </c>
@@ -12011,7 +11394,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="194" ht="38" customHeight="1" spans="1:12">
+    <row r="194" spans="1:12" ht="38" customHeight="1">
       <c r="A194" s="4">
         <v>192</v>
       </c>
@@ -12039,7 +11422,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="195" ht="38" customHeight="1" spans="1:12">
+    <row r="195" spans="1:12" ht="38" customHeight="1">
       <c r="A195" s="4">
         <v>193</v>
       </c>
@@ -12067,7 +11450,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="196" ht="38" customHeight="1" spans="1:12">
+    <row r="196" spans="1:12" ht="38" customHeight="1">
       <c r="A196" s="4">
         <v>194</v>
       </c>
@@ -12095,7 +11478,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="197" ht="38" customHeight="1" spans="1:12">
+    <row r="197" spans="1:12" ht="38" customHeight="1">
       <c r="A197" s="4">
         <v>195</v>
       </c>
@@ -12123,7 +11506,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="198" ht="38" customHeight="1" spans="1:12">
+    <row r="198" spans="1:12" ht="38" customHeight="1">
       <c r="A198" s="4">
         <v>196</v>
       </c>
@@ -12151,7 +11534,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="199" ht="38" customHeight="1" spans="1:12">
+    <row r="199" spans="1:12" ht="38" customHeight="1">
       <c r="A199" s="4">
         <v>197</v>
       </c>
@@ -12179,7 +11562,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="200" ht="38" customHeight="1" spans="1:12">
+    <row r="200" spans="1:12" ht="38" customHeight="1">
       <c r="A200" s="4">
         <v>198</v>
       </c>
@@ -12207,7 +11590,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="201" ht="38" customHeight="1" spans="1:12">
+    <row r="201" spans="1:12" ht="38" customHeight="1">
       <c r="A201" s="4">
         <v>199</v>
       </c>
@@ -12235,7 +11618,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="202" ht="38" customHeight="1" spans="1:12">
+    <row r="202" spans="1:12" ht="38" customHeight="1">
       <c r="A202" s="4">
         <v>200</v>
       </c>
@@ -12263,7 +11646,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="203" ht="38" customHeight="1" spans="1:12">
+    <row r="203" spans="1:12" ht="38" customHeight="1">
       <c r="A203" s="4">
         <v>201</v>
       </c>
@@ -12291,7 +11674,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="204" ht="38" customHeight="1" spans="1:12">
+    <row r="204" spans="1:12" ht="38" customHeight="1">
       <c r="A204" s="4">
         <v>202</v>
       </c>
@@ -12319,7 +11702,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="205" ht="38" customHeight="1" spans="1:12">
+    <row r="205" spans="1:12" ht="38" customHeight="1">
       <c r="A205" s="4">
         <v>203</v>
       </c>
@@ -12347,7 +11730,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="206" ht="38" customHeight="1" spans="1:12">
+    <row r="206" spans="1:12" ht="38" customHeight="1">
       <c r="A206" s="4">
         <v>204</v>
       </c>
@@ -12375,7 +11758,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="207" ht="38" customHeight="1" spans="1:12">
+    <row r="207" spans="1:12" ht="38" customHeight="1">
       <c r="A207" s="4">
         <v>205</v>
       </c>
@@ -12403,7 +11786,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="208" ht="38" customHeight="1" spans="1:12">
+    <row r="208" spans="1:12" ht="38" customHeight="1">
       <c r="A208" s="4">
         <v>206</v>
       </c>
@@ -12431,7 +11814,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="209" ht="38" customHeight="1" spans="1:12">
+    <row r="209" spans="1:12" ht="38" customHeight="1">
       <c r="A209" s="4">
         <v>207</v>
       </c>
@@ -12459,7 +11842,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="210" ht="38" customHeight="1" spans="1:12">
+    <row r="210" spans="1:12" ht="38" customHeight="1">
       <c r="A210" s="4">
         <v>208</v>
       </c>
@@ -12487,7 +11870,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="211" ht="38" customHeight="1" spans="1:12">
+    <row r="211" spans="1:12" ht="38" customHeight="1">
       <c r="A211" s="4">
         <v>209</v>
       </c>
@@ -12515,7 +11898,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="212" ht="38" customHeight="1" spans="1:12">
+    <row r="212" spans="1:12" ht="38" customHeight="1">
       <c r="A212" s="4">
         <v>210</v>
       </c>
@@ -12543,7 +11926,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="213" ht="38" customHeight="1" spans="1:12">
+    <row r="213" spans="1:12" ht="38" customHeight="1">
       <c r="A213" s="4">
         <v>211</v>
       </c>
@@ -12571,7 +11954,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="214" ht="38" customHeight="1" spans="1:12">
+    <row r="214" spans="1:12" ht="38" customHeight="1">
       <c r="A214" s="4">
         <v>212</v>
       </c>
@@ -12599,7 +11982,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="215" ht="38" customHeight="1" spans="1:12">
+    <row r="215" spans="1:12" ht="38" customHeight="1">
       <c r="A215" s="4">
         <v>213</v>
       </c>
@@ -12627,7 +12010,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="216" ht="38" customHeight="1" spans="1:12">
+    <row r="216" spans="1:12" ht="38" customHeight="1">
       <c r="A216" s="4">
         <v>214</v>
       </c>
@@ -12655,7 +12038,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="217" ht="38" customHeight="1" spans="1:12">
+    <row r="217" spans="1:12" ht="38" customHeight="1">
       <c r="A217" s="4">
         <v>215</v>
       </c>
@@ -12683,7 +12066,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="218" ht="38" customHeight="1" spans="1:12">
+    <row r="218" spans="1:12" ht="38" customHeight="1">
       <c r="A218" s="4">
         <v>216</v>
       </c>
@@ -12711,7 +12094,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="219" ht="38" customHeight="1" spans="1:12">
+    <row r="219" spans="1:12" ht="38" customHeight="1">
       <c r="A219" s="4">
         <v>217</v>
       </c>
@@ -12739,7 +12122,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="220" ht="38" customHeight="1" spans="1:12">
+    <row r="220" spans="1:12" ht="38" customHeight="1">
       <c r="A220" s="4">
         <v>218</v>
       </c>
@@ -12767,7 +12150,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="221" ht="38" customHeight="1" spans="1:12">
+    <row r="221" spans="1:12" ht="38" customHeight="1">
       <c r="A221" s="4">
         <v>219</v>
       </c>
@@ -12795,7 +12178,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="222" ht="38" customHeight="1" spans="1:12">
+    <row r="222" spans="1:12" ht="38" customHeight="1">
       <c r="A222" s="4">
         <v>220</v>
       </c>
@@ -12823,7 +12206,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="223" ht="38" customHeight="1" spans="1:12">
+    <row r="223" spans="1:12" ht="38" customHeight="1">
       <c r="A223" s="4">
         <v>221</v>
       </c>
@@ -12851,7 +12234,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="224" ht="38" customHeight="1" spans="1:12">
+    <row r="224" spans="1:12" ht="38" customHeight="1">
       <c r="A224" s="4">
         <v>222</v>
       </c>
@@ -12879,7 +12262,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="225" ht="38" customHeight="1" spans="1:12">
+    <row r="225" spans="1:12" ht="38" customHeight="1">
       <c r="A225" s="4">
         <v>223</v>
       </c>
@@ -12907,7 +12290,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="226" ht="38" customHeight="1" spans="1:12">
+    <row r="226" spans="1:12" ht="38" customHeight="1">
       <c r="A226" s="4">
         <v>224</v>
       </c>
@@ -12935,7 +12318,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="227" ht="38" customHeight="1" spans="1:12">
+    <row r="227" spans="1:12" ht="38" customHeight="1">
       <c r="A227" s="4">
         <v>225</v>
       </c>
@@ -12963,7 +12346,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="228" ht="38" customHeight="1" spans="1:12">
+    <row r="228" spans="1:12" ht="38" customHeight="1">
       <c r="A228" s="4">
         <v>226</v>
       </c>
@@ -12991,7 +12374,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="229" ht="38" customHeight="1" spans="1:12">
+    <row r="229" spans="1:12" ht="38" customHeight="1">
       <c r="A229" s="4">
         <v>227</v>
       </c>
@@ -13019,7 +12402,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="230" ht="38" customHeight="1" spans="1:12">
+    <row r="230" spans="1:12" ht="38" customHeight="1">
       <c r="A230" s="4">
         <v>228</v>
       </c>
@@ -13047,7 +12430,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="231" ht="38" customHeight="1" spans="1:12">
+    <row r="231" spans="1:12" ht="38" customHeight="1">
       <c r="A231" s="4">
         <v>229</v>
       </c>
@@ -13075,7 +12458,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="232" ht="38" customHeight="1" spans="1:12">
+    <row r="232" spans="1:12" ht="38" customHeight="1">
       <c r="A232" s="4">
         <v>230</v>
       </c>
@@ -13103,7 +12486,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="233" ht="38" customHeight="1" spans="1:12">
+    <row r="233" spans="1:12" ht="38" customHeight="1">
       <c r="A233" s="4">
         <v>231</v>
       </c>
@@ -13131,7 +12514,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="234" ht="38" customHeight="1" spans="1:12">
+    <row r="234" spans="1:12" ht="38" customHeight="1">
       <c r="A234" s="4">
         <v>232</v>
       </c>
@@ -13159,7 +12542,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="235" ht="38" customHeight="1" spans="1:12">
+    <row r="235" spans="1:12" ht="38" customHeight="1">
       <c r="A235" s="4">
         <v>233</v>
       </c>
@@ -13187,7 +12570,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="236" ht="38" customHeight="1" spans="1:12">
+    <row r="236" spans="1:12" ht="38" customHeight="1">
       <c r="A236" s="4">
         <v>234</v>
       </c>
@@ -13215,7 +12598,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="237" ht="38" customHeight="1" spans="1:12">
+    <row r="237" spans="1:12" ht="38" customHeight="1">
       <c r="A237" s="4">
         <v>235</v>
       </c>
@@ -13243,7 +12626,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="238" ht="38" customHeight="1" spans="1:12">
+    <row r="238" spans="1:12" ht="38" customHeight="1">
       <c r="A238" s="4">
         <v>236</v>
       </c>
@@ -13271,7 +12654,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="239" ht="38" customHeight="1" spans="1:12">
+    <row r="239" spans="1:12" ht="38" customHeight="1">
       <c r="A239" s="4">
         <v>237</v>
       </c>
@@ -13299,7 +12682,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="240" ht="38" customHeight="1" spans="1:12">
+    <row r="240" spans="1:12" ht="38" customHeight="1">
       <c r="A240" s="4">
         <v>238</v>
       </c>
@@ -13327,7 +12710,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="241" ht="38" customHeight="1" spans="1:12">
+    <row r="241" spans="1:12" ht="38" customHeight="1">
       <c r="A241" s="4">
         <v>239</v>
       </c>
@@ -13355,7 +12738,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="242" ht="38" customHeight="1" spans="1:12">
+    <row r="242" spans="1:12" ht="38" customHeight="1">
       <c r="A242" s="4">
         <v>240</v>
       </c>
@@ -13383,7 +12766,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="243" ht="38" customHeight="1" spans="1:12">
+    <row r="243" spans="1:12" ht="38" customHeight="1">
       <c r="A243" s="4">
         <v>241</v>
       </c>
@@ -13411,7 +12794,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="244" ht="38" customHeight="1" spans="1:12">
+    <row r="244" spans="1:12" ht="38" customHeight="1">
       <c r="A244" s="4">
         <v>242</v>
       </c>
@@ -13439,7 +12822,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="245" ht="38" customHeight="1" spans="1:12">
+    <row r="245" spans="1:12" ht="38" customHeight="1">
       <c r="A245" s="4">
         <v>243</v>
       </c>
@@ -13467,7 +12850,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="246" ht="38" customHeight="1" spans="1:12">
+    <row r="246" spans="1:12" ht="38" customHeight="1">
       <c r="A246" s="4">
         <v>244</v>
       </c>
@@ -13495,7 +12878,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="247" ht="38" customHeight="1" spans="1:12">
+    <row r="247" spans="1:12" ht="38" customHeight="1">
       <c r="A247" s="4">
         <v>245</v>
       </c>
@@ -13523,7 +12906,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="248" ht="38" customHeight="1" spans="1:12">
+    <row r="248" spans="1:12" ht="38" customHeight="1">
       <c r="A248" s="4">
         <v>246</v>
       </c>
@@ -13551,7 +12934,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="249" ht="38" customHeight="1" spans="1:12">
+    <row r="249" spans="1:12" ht="38" customHeight="1">
       <c r="A249" s="4">
         <v>247</v>
       </c>
@@ -13579,7 +12962,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="250" ht="38" customHeight="1" spans="1:12">
+    <row r="250" spans="1:12" ht="38" customHeight="1">
       <c r="A250" s="4">
         <v>248</v>
       </c>
@@ -13607,7 +12990,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="251" ht="38" customHeight="1" spans="1:12">
+    <row r="251" spans="1:12" ht="38" customHeight="1">
       <c r="A251" s="4">
         <v>249</v>
       </c>
@@ -13635,7 +13018,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="252" ht="38" customHeight="1" spans="1:12">
+    <row r="252" spans="1:12" ht="38" customHeight="1">
       <c r="A252" s="4">
         <v>250</v>
       </c>
@@ -13663,7 +13046,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="253" ht="38" customHeight="1" spans="1:12">
+    <row r="253" spans="1:12" ht="38" customHeight="1">
       <c r="A253" s="4">
         <v>251</v>
       </c>
@@ -13691,7 +13074,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="254" ht="38" customHeight="1" spans="1:12">
+    <row r="254" spans="1:12" ht="38" customHeight="1">
       <c r="A254" s="4">
         <v>252</v>
       </c>
@@ -13719,7 +13102,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="255" ht="38" customHeight="1" spans="1:12">
+    <row r="255" spans="1:12" ht="38" customHeight="1">
       <c r="A255" s="4">
         <v>253</v>
       </c>
@@ -13747,7 +13130,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="256" ht="38" customHeight="1" spans="1:12">
+    <row r="256" spans="1:12" ht="38" customHeight="1">
       <c r="A256" s="4">
         <v>254</v>
       </c>
@@ -13775,7 +13158,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="257" ht="38" customHeight="1" spans="1:12">
+    <row r="257" spans="1:12" ht="38" customHeight="1">
       <c r="A257" s="4">
         <v>255</v>
       </c>
@@ -13803,7 +13186,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="258" ht="38" customHeight="1" spans="1:12">
+    <row r="258" spans="1:12" ht="38" customHeight="1">
       <c r="A258" s="4">
         <v>256</v>
       </c>
@@ -13831,7 +13214,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="259" ht="38" customHeight="1" spans="1:12">
+    <row r="259" spans="1:12" ht="38" customHeight="1">
       <c r="A259" s="4">
         <v>257</v>
       </c>
@@ -13859,7 +13242,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="260" ht="38" customHeight="1" spans="1:12">
+    <row r="260" spans="1:12" ht="38" customHeight="1">
       <c r="A260" s="4">
         <v>258</v>
       </c>
@@ -13887,7 +13270,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="261" ht="38" customHeight="1" spans="1:12">
+    <row r="261" spans="1:12" ht="38" customHeight="1">
       <c r="A261" s="4">
         <v>259</v>
       </c>
@@ -13915,7 +13298,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="262" ht="38" customHeight="1" spans="1:12">
+    <row r="262" spans="1:12" ht="38" customHeight="1">
       <c r="A262" s="4">
         <v>260</v>
       </c>
@@ -13943,7 +13326,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="263" ht="38" customHeight="1" spans="1:12">
+    <row r="263" spans="1:12" ht="38" customHeight="1">
       <c r="A263" s="4">
         <v>261</v>
       </c>
@@ -13971,7 +13354,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="264" ht="38" customHeight="1" spans="1:12">
+    <row r="264" spans="1:12" ht="38" customHeight="1">
       <c r="A264" s="4">
         <v>262</v>
       </c>
@@ -13999,7 +13382,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="265" ht="38" customHeight="1" spans="1:12">
+    <row r="265" spans="1:12" ht="38" customHeight="1">
       <c r="A265" s="4">
         <v>263</v>
       </c>
@@ -14027,7 +13410,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="266" ht="38" customHeight="1" spans="1:12">
+    <row r="266" spans="1:12" ht="38" customHeight="1">
       <c r="A266" s="4">
         <v>264</v>
       </c>
@@ -14055,7 +13438,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="267" ht="38" customHeight="1" spans="1:12">
+    <row r="267" spans="1:12" ht="38" customHeight="1">
       <c r="A267" s="4">
         <v>265</v>
       </c>
@@ -14083,7 +13466,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="268" ht="38" customHeight="1" spans="1:12">
+    <row r="268" spans="1:12" ht="38" customHeight="1">
       <c r="A268" s="4">
         <v>266</v>
       </c>
@@ -14111,7 +13494,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="269" ht="38" customHeight="1" spans="1:12">
+    <row r="269" spans="1:12" ht="38" customHeight="1">
       <c r="A269" s="4">
         <v>267</v>
       </c>
@@ -14139,7 +13522,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="270" ht="38" customHeight="1" spans="1:12">
+    <row r="270" spans="1:12" ht="38" customHeight="1">
       <c r="A270" s="4">
         <v>268</v>
       </c>
@@ -14167,7 +13550,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="271" ht="38" customHeight="1" spans="1:12">
+    <row r="271" spans="1:12" ht="38" customHeight="1">
       <c r="A271" s="4">
         <v>269</v>
       </c>
@@ -14195,7 +13578,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="272" ht="38" customHeight="1" spans="1:12">
+    <row r="272" spans="1:12" ht="38" customHeight="1">
       <c r="A272" s="4">
         <v>270</v>
       </c>
@@ -14223,7 +13606,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="273" ht="38" customHeight="1" spans="1:12">
+    <row r="273" spans="1:12" ht="38" customHeight="1">
       <c r="A273" s="4">
         <v>271</v>
       </c>
@@ -14251,7 +13634,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="274" ht="38" customHeight="1" spans="1:12">
+    <row r="274" spans="1:12" ht="38" customHeight="1">
       <c r="A274" s="4">
         <v>272</v>
       </c>
@@ -14279,7 +13662,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="275" ht="38" customHeight="1" spans="1:12">
+    <row r="275" spans="1:12" ht="38" customHeight="1">
       <c r="A275" s="4">
         <v>273</v>
       </c>
@@ -14307,7 +13690,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="276" ht="38" customHeight="1" spans="1:12">
+    <row r="276" spans="1:12" ht="38" customHeight="1">
       <c r="A276" s="4">
         <v>274</v>
       </c>
@@ -14335,7 +13718,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="277" ht="38" customHeight="1" spans="1:12">
+    <row r="277" spans="1:12" ht="38" customHeight="1">
       <c r="A277" s="4">
         <v>275</v>
       </c>
@@ -14363,7 +13746,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="278" ht="38" customHeight="1" spans="1:12">
+    <row r="278" spans="1:12" ht="38" customHeight="1">
       <c r="A278" s="4">
         <v>276</v>
       </c>
@@ -14391,7 +13774,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="279" ht="38" customHeight="1" spans="1:12">
+    <row r="279" spans="1:12" ht="38" customHeight="1">
       <c r="A279" s="4">
         <v>277</v>
       </c>
@@ -14419,7 +13802,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="280" ht="38" customHeight="1" spans="1:12">
+    <row r="280" spans="1:12" ht="38" customHeight="1">
       <c r="A280" s="4">
         <v>278</v>
       </c>
@@ -14447,7 +13830,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="281" ht="38" customHeight="1" spans="1:12">
+    <row r="281" spans="1:12" ht="38" customHeight="1">
       <c r="A281" s="4">
         <v>279</v>
       </c>
@@ -14475,7 +13858,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="282" ht="38" customHeight="1" spans="1:12">
+    <row r="282" spans="1:12" ht="38" customHeight="1">
       <c r="A282" s="4">
         <v>280</v>
       </c>
@@ -14503,7 +13886,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="283" ht="38" customHeight="1" spans="1:12">
+    <row r="283" spans="1:12" ht="38" customHeight="1">
       <c r="A283" s="4">
         <v>281</v>
       </c>
@@ -14531,7 +13914,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="284" ht="38" customHeight="1" spans="1:12">
+    <row r="284" spans="1:12" ht="38" customHeight="1">
       <c r="A284" s="4">
         <v>282</v>
       </c>
@@ -14559,7 +13942,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="285" ht="38" customHeight="1" spans="1:12">
+    <row r="285" spans="1:12" ht="38" customHeight="1">
       <c r="A285" s="4">
         <v>283</v>
       </c>
@@ -14587,7 +13970,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="286" ht="38" customHeight="1" spans="1:12">
+    <row r="286" spans="1:12" ht="38" customHeight="1">
       <c r="A286" s="4">
         <v>284</v>
       </c>
@@ -14615,7 +13998,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="287" ht="38" customHeight="1" spans="1:12">
+    <row r="287" spans="1:12" ht="38" customHeight="1">
       <c r="A287" s="4">
         <v>285</v>
       </c>
@@ -14643,7 +14026,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="288" ht="38" customHeight="1" spans="1:12">
+    <row r="288" spans="1:12" ht="38" customHeight="1">
       <c r="A288" s="4">
         <v>286</v>
       </c>
@@ -14671,7 +14054,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="289" ht="38" customHeight="1" spans="1:12">
+    <row r="289" spans="1:12" ht="38" customHeight="1">
       <c r="A289" s="4">
         <v>287</v>
       </c>
@@ -14699,7 +14082,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="290" ht="38" customHeight="1" spans="1:12">
+    <row r="290" spans="1:12" ht="38" customHeight="1">
       <c r="A290" s="4">
         <v>288</v>
       </c>
@@ -14727,7 +14110,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="291" ht="38" customHeight="1" spans="1:12">
+    <row r="291" spans="1:12" ht="38" customHeight="1">
       <c r="A291" s="4">
         <v>289</v>
       </c>
@@ -14755,7 +14138,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="292" ht="38" customHeight="1" spans="1:12">
+    <row r="292" spans="1:12" ht="38" customHeight="1">
       <c r="A292" s="4">
         <v>290</v>
       </c>
@@ -14783,7 +14166,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="293" ht="38" customHeight="1" spans="1:12">
+    <row r="293" spans="1:12" ht="38" customHeight="1">
       <c r="A293" s="4">
         <v>291</v>
       </c>
@@ -14811,7 +14194,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="294" ht="38" customHeight="1" spans="1:12">
+    <row r="294" spans="1:12" ht="38" customHeight="1">
       <c r="A294" s="4">
         <v>292</v>
       </c>
@@ -14839,7 +14222,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="295" ht="38" customHeight="1" spans="1:12">
+    <row r="295" spans="1:12" ht="38" customHeight="1">
       <c r="A295" s="4">
         <v>293</v>
       </c>
@@ -14867,7 +14250,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="296" ht="38" customHeight="1" spans="1:12">
+    <row r="296" spans="1:12" ht="38" customHeight="1">
       <c r="A296" s="4">
         <v>294</v>
       </c>
@@ -14895,7 +14278,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="297" ht="38" customHeight="1" spans="1:12">
+    <row r="297" spans="1:12" ht="38" customHeight="1">
       <c r="A297" s="4">
         <v>295</v>
       </c>
@@ -14923,7 +14306,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="298" ht="38" customHeight="1" spans="1:12">
+    <row r="298" spans="1:12" ht="38" customHeight="1">
       <c r="A298" s="4">
         <v>296</v>
       </c>
@@ -14951,7 +14334,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="299" ht="38" customHeight="1" spans="1:12">
+    <row r="299" spans="1:12" ht="38" customHeight="1">
       <c r="A299" s="4">
         <v>297</v>
       </c>
@@ -14979,7 +14362,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="300" ht="38" customHeight="1" spans="1:12">
+    <row r="300" spans="1:12" ht="38" customHeight="1">
       <c r="A300" s="4">
         <v>298</v>
       </c>
@@ -15007,7 +14390,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="301" ht="38" customHeight="1" spans="1:12">
+    <row r="301" spans="1:12" ht="38" customHeight="1">
       <c r="A301" s="4">
         <v>299</v>
       </c>
@@ -15035,7 +14418,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="302" ht="38" customHeight="1" spans="1:12">
+    <row r="302" spans="1:12" ht="38" customHeight="1">
       <c r="A302" s="4">
         <v>300</v>
       </c>
@@ -15063,7 +14446,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="303" ht="38" customHeight="1" spans="1:12">
+    <row r="303" spans="1:12" ht="38" customHeight="1">
       <c r="A303" s="4">
         <v>301</v>
       </c>
@@ -15091,7 +14474,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="304" ht="38" customHeight="1" spans="1:12">
+    <row r="304" spans="1:12" ht="38" customHeight="1">
       <c r="A304" s="4">
         <v>302</v>
       </c>
@@ -15119,7 +14502,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="305" ht="38" customHeight="1" spans="1:12">
+    <row r="305" spans="1:12" ht="38" customHeight="1">
       <c r="A305" s="4">
         <v>303</v>
       </c>
@@ -15147,7 +14530,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="306" ht="38" customHeight="1" spans="1:12">
+    <row r="306" spans="1:12" ht="38" customHeight="1">
       <c r="A306" s="4">
         <v>304</v>
       </c>
@@ -15175,7 +14558,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="307" ht="38" customHeight="1" spans="1:12">
+    <row r="307" spans="1:12" ht="38" customHeight="1">
       <c r="A307" s="4">
         <v>305</v>
       </c>
@@ -15203,7 +14586,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="308" ht="38" customHeight="1" spans="1:12">
+    <row r="308" spans="1:12" ht="38" customHeight="1">
       <c r="A308" s="4">
         <v>306</v>
       </c>
@@ -15231,7 +14614,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="309" ht="38" customHeight="1" spans="1:12">
+    <row r="309" spans="1:12" ht="38" customHeight="1">
       <c r="A309" s="4">
         <v>307</v>
       </c>
@@ -15259,7 +14642,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="310" ht="38" customHeight="1" spans="1:12">
+    <row r="310" spans="1:12" ht="38" customHeight="1">
       <c r="A310" s="4">
         <v>308</v>
       </c>
@@ -15287,7 +14670,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="311" ht="38" customHeight="1" spans="1:12">
+    <row r="311" spans="1:12" ht="38" customHeight="1">
       <c r="A311" s="4">
         <v>309</v>
       </c>
@@ -15315,7 +14698,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="312" ht="38" customHeight="1" spans="1:12">
+    <row r="312" spans="1:12" ht="38" customHeight="1">
       <c r="A312" s="4">
         <v>310</v>
       </c>
@@ -15343,7 +14726,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="313" ht="38" customHeight="1" spans="1:12">
+    <row r="313" spans="1:12" ht="38" customHeight="1">
       <c r="A313" s="4">
         <v>311</v>
       </c>
@@ -15371,7 +14754,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="314" ht="38" customHeight="1" spans="1:12">
+    <row r="314" spans="1:12" ht="38" customHeight="1">
       <c r="A314" s="4">
         <v>312</v>
       </c>
@@ -15399,7 +14782,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="315" ht="38" customHeight="1" spans="1:12">
+    <row r="315" spans="1:12" ht="38" customHeight="1">
       <c r="A315" s="4">
         <v>313</v>
       </c>
@@ -15427,7 +14810,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="316" ht="38" customHeight="1" spans="1:12">
+    <row r="316" spans="1:12" ht="38" customHeight="1">
       <c r="A316" s="4">
         <v>314</v>
       </c>
@@ -15455,7 +14838,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="317" ht="38" customHeight="1" spans="1:12">
+    <row r="317" spans="1:12" ht="38" customHeight="1">
       <c r="A317" s="4">
         <v>315</v>
       </c>
@@ -15483,7 +14866,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="318" ht="38" customHeight="1" spans="1:12">
+    <row r="318" spans="1:12" ht="38" customHeight="1">
       <c r="A318" s="4">
         <v>316</v>
       </c>
@@ -15511,7 +14894,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="319" ht="38" customHeight="1" spans="1:12">
+    <row r="319" spans="1:12" ht="38" customHeight="1">
       <c r="A319" s="4">
         <v>317</v>
       </c>
@@ -15539,7 +14922,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="320" ht="38" customHeight="1" spans="1:12">
+    <row r="320" spans="1:12" ht="38" customHeight="1">
       <c r="A320" s="4">
         <v>318</v>
       </c>
@@ -15567,7 +14950,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="321" ht="38" customHeight="1" spans="1:12">
+    <row r="321" spans="1:12" ht="38" customHeight="1">
       <c r="A321" s="4">
         <v>319</v>
       </c>
@@ -15595,7 +14978,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="322" ht="38" customHeight="1" spans="1:12">
+    <row r="322" spans="1:12" ht="38" customHeight="1">
       <c r="A322" s="4">
         <v>320</v>
       </c>
@@ -15623,7 +15006,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="323" ht="38" customHeight="1" spans="1:12">
+    <row r="323" spans="1:12" ht="38" customHeight="1">
       <c r="A323" s="4">
         <v>321</v>
       </c>
@@ -15651,7 +15034,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="324" ht="38" customHeight="1" spans="1:12">
+    <row r="324" spans="1:12" ht="38" customHeight="1">
       <c r="A324" s="4">
         <v>322</v>
       </c>
@@ -15679,7 +15062,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="325" ht="38" customHeight="1" spans="1:12">
+    <row r="325" spans="1:12" ht="38" customHeight="1">
       <c r="A325" s="4">
         <v>323</v>
       </c>
@@ -15707,7 +15090,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="326" ht="38" customHeight="1" spans="1:12">
+    <row r="326" spans="1:12" ht="38" customHeight="1">
       <c r="A326" s="4">
         <v>324</v>
       </c>
@@ -15735,7 +15118,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="327" ht="38" customHeight="1" spans="1:12">
+    <row r="327" spans="1:12" ht="38" customHeight="1">
       <c r="A327" s="4">
         <v>325</v>
       </c>
@@ -15763,7 +15146,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="328" ht="38" customHeight="1" spans="1:12">
+    <row r="328" spans="1:12" ht="38" customHeight="1">
       <c r="A328" s="4">
         <v>326</v>
       </c>
@@ -15791,7 +15174,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="329" ht="38" customHeight="1" spans="1:12">
+    <row r="329" spans="1:12" ht="38" customHeight="1">
       <c r="A329" s="4">
         <v>327</v>
       </c>
@@ -15819,7 +15202,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="330" ht="38" customHeight="1" spans="1:12">
+    <row r="330" spans="1:12" ht="38" customHeight="1">
       <c r="A330" s="4">
         <v>328</v>
       </c>
@@ -15847,7 +15230,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="331" ht="38" customHeight="1" spans="1:12">
+    <row r="331" spans="1:12" ht="38" customHeight="1">
       <c r="A331" s="4">
         <v>329</v>
       </c>
@@ -15875,7 +15258,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="332" ht="38" customHeight="1" spans="1:12">
+    <row r="332" spans="1:12" ht="38" customHeight="1">
       <c r="A332" s="4">
         <v>330</v>
       </c>
@@ -15903,7 +15286,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="333" ht="38" customHeight="1" spans="1:12">
+    <row r="333" spans="1:12" ht="38" customHeight="1">
       <c r="A333" s="4">
         <v>331</v>
       </c>
@@ -15931,7 +15314,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="334" ht="38" customHeight="1" spans="1:12">
+    <row r="334" spans="1:12" ht="38" customHeight="1">
       <c r="A334" s="4">
         <v>332</v>
       </c>
@@ -15959,7 +15342,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="335" ht="38" customHeight="1" spans="1:12">
+    <row r="335" spans="1:12" ht="38" customHeight="1">
       <c r="A335" s="4">
         <v>333</v>
       </c>
@@ -15987,7 +15370,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="336" ht="38" customHeight="1" spans="1:12">
+    <row r="336" spans="1:12" ht="38" customHeight="1">
       <c r="A336" s="4">
         <v>334</v>
       </c>
@@ -16015,7 +15398,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="337" ht="38" customHeight="1" spans="1:12">
+    <row r="337" spans="1:12" ht="38" customHeight="1">
       <c r="A337" s="4">
         <v>335</v>
       </c>
@@ -16043,7 +15426,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="338" ht="38" customHeight="1" spans="1:12">
+    <row r="338" spans="1:12" ht="38" customHeight="1">
       <c r="A338" s="4">
         <v>336</v>
       </c>
@@ -16071,7 +15454,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="339" ht="38" customHeight="1" spans="1:12">
+    <row r="339" spans="1:12" ht="38" customHeight="1">
       <c r="A339" s="4">
         <v>337</v>
       </c>
@@ -16099,7 +15482,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="340" ht="38" customHeight="1" spans="1:12">
+    <row r="340" spans="1:12" ht="38" customHeight="1">
       <c r="A340" s="4">
         <v>338</v>
       </c>
@@ -16127,7 +15510,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="341" ht="38" customHeight="1" spans="1:12">
+    <row r="341" spans="1:12" ht="38" customHeight="1">
       <c r="A341" s="4">
         <v>339</v>
       </c>
@@ -16155,7 +15538,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="342" ht="38" customHeight="1" spans="1:12">
+    <row r="342" spans="1:12" ht="38" customHeight="1">
       <c r="A342" s="4">
         <v>340</v>
       </c>
@@ -16183,7 +15566,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="343" ht="38" customHeight="1" spans="1:12">
+    <row r="343" spans="1:12" ht="38" customHeight="1">
       <c r="A343" s="4">
         <v>341</v>
       </c>
@@ -16211,7 +15594,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="344" ht="38" customHeight="1" spans="1:12">
+    <row r="344" spans="1:12" ht="38" customHeight="1">
       <c r="A344" s="4">
         <v>342</v>
       </c>
@@ -16239,7 +15622,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="345" ht="38" customHeight="1" spans="1:12">
+    <row r="345" spans="1:12" ht="38" customHeight="1">
       <c r="A345" s="4">
         <v>343</v>
       </c>
@@ -16267,7 +15650,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="346" ht="38" customHeight="1" spans="1:12">
+    <row r="346" spans="1:12" ht="38" customHeight="1">
       <c r="A346" s="4">
         <v>344</v>
       </c>
@@ -16295,7 +15678,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="347" ht="38" customHeight="1" spans="1:12">
+    <row r="347" spans="1:12" ht="38" customHeight="1">
       <c r="A347" s="4">
         <v>345</v>
       </c>
@@ -16323,7 +15706,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="348" ht="38" customHeight="1" spans="1:12">
+    <row r="348" spans="1:12" ht="38" customHeight="1">
       <c r="A348" s="4">
         <v>346</v>
       </c>
@@ -16351,7 +15734,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="349" ht="38" customHeight="1" spans="1:12">
+    <row r="349" spans="1:12" ht="38" customHeight="1">
       <c r="A349" s="4">
         <v>347</v>
       </c>
@@ -16379,7 +15762,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="350" ht="38" customHeight="1" spans="1:12">
+    <row r="350" spans="1:12" ht="38" customHeight="1">
       <c r="A350" s="4">
         <v>348</v>
       </c>
@@ -16407,7 +15790,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="351" ht="38" customHeight="1" spans="1:12">
+    <row r="351" spans="1:12" ht="38" customHeight="1">
       <c r="A351" s="4">
         <v>349</v>
       </c>
@@ -16435,7 +15818,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="352" ht="38" customHeight="1" spans="1:12">
+    <row r="352" spans="1:12" ht="38" customHeight="1">
       <c r="A352" s="4">
         <v>350</v>
       </c>
@@ -16463,7 +15846,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="353" ht="38" customHeight="1" spans="1:12">
+    <row r="353" spans="1:12" ht="38" customHeight="1">
       <c r="A353" s="4">
         <v>351</v>
       </c>
@@ -16491,7 +15874,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="354" ht="38" customHeight="1" spans="1:12">
+    <row r="354" spans="1:12" ht="38" customHeight="1">
       <c r="A354" s="4">
         <v>352</v>
       </c>
@@ -16519,7 +15902,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="355" ht="38" customHeight="1" spans="1:12">
+    <row r="355" spans="1:12" ht="38" customHeight="1">
       <c r="A355" s="4">
         <v>353</v>
       </c>
@@ -16547,7 +15930,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="356" ht="38" customHeight="1" spans="1:12">
+    <row r="356" spans="1:12" ht="38" customHeight="1">
       <c r="A356" s="4">
         <v>354</v>
       </c>
@@ -16575,7 +15958,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="357" ht="38" customHeight="1" spans="1:12">
+    <row r="357" spans="1:12" ht="38" customHeight="1">
       <c r="A357" s="4">
         <v>355</v>
       </c>
@@ -16603,7 +15986,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="358" ht="38" customHeight="1" spans="1:12">
+    <row r="358" spans="1:12" ht="38" customHeight="1">
       <c r="A358" s="4">
         <v>356</v>
       </c>
@@ -16631,7 +16014,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="359" ht="38" customHeight="1" spans="1:12">
+    <row r="359" spans="1:12" ht="38" customHeight="1">
       <c r="A359" s="4">
         <v>357</v>
       </c>
@@ -16659,7 +16042,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="360" ht="38" customHeight="1" spans="1:12">
+    <row r="360" spans="1:12" ht="38" customHeight="1">
       <c r="A360" s="4">
         <v>358</v>
       </c>
@@ -16687,7 +16070,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="361" ht="38" customHeight="1" spans="1:12">
+    <row r="361" spans="1:12" ht="38" customHeight="1">
       <c r="A361" s="4">
         <v>359</v>
       </c>
@@ -16715,7 +16098,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="362" ht="38" customHeight="1" spans="1:12">
+    <row r="362" spans="1:12" ht="38" customHeight="1">
       <c r="A362" s="4">
         <v>360</v>
       </c>
@@ -16743,7 +16126,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="363" ht="38" customHeight="1" spans="1:12">
+    <row r="363" spans="1:12" ht="38" customHeight="1">
       <c r="A363" s="4">
         <v>361</v>
       </c>
@@ -16771,7 +16154,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="364" ht="38" customHeight="1" spans="1:12">
+    <row r="364" spans="1:12" ht="38" customHeight="1">
       <c r="A364" s="4">
         <v>362</v>
       </c>
@@ -16799,7 +16182,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="365" ht="38" customHeight="1" spans="1:12">
+    <row r="365" spans="1:12" ht="38" customHeight="1">
       <c r="A365" s="4">
         <v>363</v>
       </c>
@@ -16827,7 +16210,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="366" ht="38" customHeight="1" spans="1:12">
+    <row r="366" spans="1:12" ht="38" customHeight="1">
       <c r="A366" s="4">
         <v>364</v>
       </c>
@@ -16855,7 +16238,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="367" ht="38" customHeight="1" spans="1:12">
+    <row r="367" spans="1:12" ht="38" customHeight="1">
       <c r="A367" s="4">
         <v>365</v>
       </c>
@@ -16883,7 +16266,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="368" ht="38" customHeight="1" spans="1:12">
+    <row r="368" spans="1:12" ht="38" customHeight="1">
       <c r="A368" s="4">
         <v>366</v>
       </c>
@@ -16911,7 +16294,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="369" ht="38" customHeight="1" spans="1:12">
+    <row r="369" spans="1:12" ht="38" customHeight="1">
       <c r="A369" s="4">
         <v>367</v>
       </c>
@@ -16939,7 +16322,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="370" ht="38" customHeight="1" spans="1:12">
+    <row r="370" spans="1:12" ht="38" customHeight="1">
       <c r="A370" s="4">
         <v>368</v>
       </c>
@@ -16967,7 +16350,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="371" ht="38" customHeight="1" spans="1:12">
+    <row r="371" spans="1:12" ht="38" customHeight="1">
       <c r="A371" s="4">
         <v>369</v>
       </c>
@@ -16995,7 +16378,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="372" ht="38" customHeight="1" spans="1:12">
+    <row r="372" spans="1:12" ht="38" customHeight="1">
       <c r="A372" s="4">
         <v>370</v>
       </c>
@@ -17023,7 +16406,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="373" ht="38" customHeight="1" spans="1:12">
+    <row r="373" spans="1:12" ht="38" customHeight="1">
       <c r="A373" s="4">
         <v>371</v>
       </c>
@@ -17051,7 +16434,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="374" ht="38" customHeight="1" spans="1:12">
+    <row r="374" spans="1:12" ht="38" customHeight="1">
       <c r="A374" s="4">
         <v>372</v>
       </c>
@@ -17079,7 +16462,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="375" ht="38" customHeight="1" spans="1:12">
+    <row r="375" spans="1:12" ht="38" customHeight="1">
       <c r="A375" s="4">
         <v>373</v>
       </c>
@@ -17107,7 +16490,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="376" ht="38" customHeight="1" spans="1:12">
+    <row r="376" spans="1:12" ht="38" customHeight="1">
       <c r="A376" s="4">
         <v>374</v>
       </c>
@@ -17133,7 +16516,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="377" ht="38" customHeight="1" spans="1:12">
+    <row r="377" spans="1:12" ht="38" customHeight="1">
       <c r="A377" s="4">
         <v>375</v>
       </c>
@@ -17159,7 +16542,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="378" ht="38" customHeight="1" spans="1:12">
+    <row r="378" spans="1:12" ht="38" customHeight="1">
       <c r="A378" s="4">
         <v>376</v>
       </c>
@@ -17187,7 +16570,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="379" ht="38" customHeight="1" spans="1:12">
+    <row r="379" spans="1:12" ht="38" customHeight="1">
       <c r="A379" s="4">
         <v>377</v>
       </c>
@@ -17215,7 +16598,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="380" ht="38" customHeight="1" spans="1:12">
+    <row r="380" spans="1:12" ht="38" customHeight="1">
       <c r="A380" s="4">
         <v>378</v>
       </c>
@@ -17243,7 +16626,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="381" ht="38" customHeight="1" spans="1:12">
+    <row r="381" spans="1:12" ht="38" customHeight="1">
       <c r="A381" s="4">
         <v>379</v>
       </c>
@@ -17271,7 +16654,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="382" ht="38" customHeight="1" spans="1:12">
+    <row r="382" spans="1:12" ht="38" customHeight="1">
       <c r="A382" s="4">
         <v>380</v>
       </c>
@@ -17299,7 +16682,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="383" ht="38" customHeight="1" spans="1:12">
+    <row r="383" spans="1:12" ht="38" customHeight="1">
       <c r="A383" s="4">
         <v>381</v>
       </c>
@@ -17327,7 +16710,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="384" ht="38" customHeight="1" spans="1:12">
+    <row r="384" spans="1:12" ht="38" customHeight="1">
       <c r="A384" s="4">
         <v>382</v>
       </c>
@@ -17353,7 +16736,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="385" ht="38" customHeight="1" spans="1:12">
+    <row r="385" spans="1:12" ht="38" customHeight="1">
       <c r="A385" s="4">
         <v>383</v>
       </c>
@@ -17381,7 +16764,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="386" ht="38" customHeight="1" spans="1:12">
+    <row r="386" spans="1:12" ht="38" customHeight="1">
       <c r="A386" s="4">
         <v>384</v>
       </c>
@@ -17409,7 +16792,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="387" ht="38" customHeight="1" spans="1:12">
+    <row r="387" spans="1:12" ht="38" customHeight="1">
       <c r="A387" s="4">
         <v>385</v>
       </c>
@@ -17437,7 +16820,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="388" ht="38" customHeight="1" spans="1:12">
+    <row r="388" spans="1:12" ht="38" customHeight="1">
       <c r="A388" s="4">
         <v>386</v>
       </c>
@@ -17465,7 +16848,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="389" ht="38" customHeight="1" spans="1:12">
+    <row r="389" spans="1:12" ht="38" customHeight="1">
       <c r="A389" s="4">
         <v>387</v>
       </c>
@@ -17493,7 +16876,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="390" ht="38" customHeight="1" spans="1:12">
+    <row r="390" spans="1:12" ht="38" customHeight="1">
       <c r="A390" s="4">
         <v>388</v>
       </c>
@@ -17521,7 +16904,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="391" ht="38" customHeight="1" spans="1:12">
+    <row r="391" spans="1:12" ht="38" customHeight="1">
       <c r="A391" s="4">
         <v>389</v>
       </c>
@@ -17549,7 +16932,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="392" ht="38" customHeight="1" spans="1:12">
+    <row r="392" spans="1:12" ht="38" customHeight="1">
       <c r="A392" s="4">
         <v>390</v>
       </c>
@@ -17577,7 +16960,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="393" ht="38" customHeight="1" spans="1:12">
+    <row r="393" spans="1:12" ht="38" customHeight="1">
       <c r="A393" s="4">
         <v>391</v>
       </c>
@@ -17605,7 +16988,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="394" ht="38" customHeight="1" spans="1:12">
+    <row r="394" spans="1:12" ht="38" customHeight="1">
       <c r="A394" s="4">
         <v>392</v>
       </c>
@@ -17633,7 +17016,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="395" ht="38" customHeight="1" spans="1:12">
+    <row r="395" spans="1:12" ht="38" customHeight="1">
       <c r="A395" s="4">
         <v>393</v>
       </c>
@@ -17661,7 +17044,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="396" ht="38" customHeight="1" spans="1:12">
+    <row r="396" spans="1:12" ht="38" customHeight="1">
       <c r="A396" s="4">
         <v>394</v>
       </c>
@@ -17689,7 +17072,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="397" ht="38" customHeight="1" spans="1:12">
+    <row r="397" spans="1:12" ht="38" customHeight="1">
       <c r="A397" s="4">
         <v>395</v>
       </c>
@@ -17717,7 +17100,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="398" ht="38" customHeight="1" spans="1:12">
+    <row r="398" spans="1:12" ht="38" customHeight="1">
       <c r="A398" s="4">
         <v>396</v>
       </c>
@@ -17745,7 +17128,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="399" ht="38" customHeight="1" spans="1:12">
+    <row r="399" spans="1:12" ht="38" customHeight="1">
       <c r="A399" s="4">
         <v>397</v>
       </c>
@@ -17773,7 +17156,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="400" ht="38" customHeight="1" spans="1:12">
+    <row r="400" spans="1:12" ht="38" customHeight="1">
       <c r="A400" s="4">
         <v>398</v>
       </c>
@@ -17801,7 +17184,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="401" ht="38" customHeight="1" spans="1:12">
+    <row r="401" spans="1:12" ht="38" customHeight="1">
       <c r="A401" s="4">
         <v>399</v>
       </c>
@@ -17829,7 +17212,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="402" ht="38" customHeight="1" spans="1:12">
+    <row r="402" spans="1:12" ht="38" customHeight="1">
       <c r="A402" s="4">
         <v>400</v>
       </c>
@@ -17857,7 +17240,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="403" ht="38" customHeight="1" spans="1:12">
+    <row r="403" spans="1:12" ht="38" customHeight="1">
       <c r="A403" s="4">
         <v>401</v>
       </c>
@@ -17885,7 +17268,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="404" ht="38" customHeight="1" spans="1:12">
+    <row r="404" spans="1:12" ht="38" customHeight="1">
       <c r="A404" s="4">
         <v>402</v>
       </c>
@@ -17913,7 +17296,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="405" ht="38" customHeight="1" spans="1:12">
+    <row r="405" spans="1:12" ht="38" customHeight="1">
       <c r="A405" s="4">
         <v>403</v>
       </c>
@@ -17941,7 +17324,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="406" ht="38" customHeight="1" spans="1:12">
+    <row r="406" spans="1:12" ht="38" customHeight="1">
       <c r="A406" s="4">
         <v>404</v>
       </c>
@@ -17969,7 +17352,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="407" ht="38" customHeight="1" spans="1:12">
+    <row r="407" spans="1:12" ht="38" customHeight="1">
       <c r="A407" s="4">
         <v>405</v>
       </c>
@@ -17997,7 +17380,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="408" ht="38" customHeight="1" spans="1:12">
+    <row r="408" spans="1:12" ht="38" customHeight="1">
       <c r="A408" s="4">
         <v>406</v>
       </c>
@@ -18025,7 +17408,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="409" ht="38" customHeight="1" spans="1:12">
+    <row r="409" spans="1:12" ht="38" customHeight="1">
       <c r="A409" s="4">
         <v>407</v>
       </c>
@@ -18053,7 +17436,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="410" ht="38" customHeight="1" spans="1:12">
+    <row r="410" spans="1:12" ht="38" customHeight="1">
       <c r="A410" s="4">
         <v>408</v>
       </c>
@@ -18081,7 +17464,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="411" ht="38" customHeight="1" spans="1:12">
+    <row r="411" spans="1:12" ht="38" customHeight="1">
       <c r="A411" s="4">
         <v>409</v>
       </c>
@@ -18109,7 +17492,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="412" ht="38" customHeight="1" spans="1:12">
+    <row r="412" spans="1:12" ht="38" customHeight="1">
       <c r="A412" s="4">
         <v>410</v>
       </c>
@@ -18137,7 +17520,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="413" ht="38" customHeight="1" spans="1:12">
+    <row r="413" spans="1:12" ht="38" customHeight="1">
       <c r="A413" s="4">
         <v>411</v>
       </c>
@@ -18165,7 +17548,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="414" ht="38" customHeight="1" spans="1:12">
+    <row r="414" spans="1:12" ht="38" customHeight="1">
       <c r="A414" s="4">
         <v>412</v>
       </c>
@@ -18193,7 +17576,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="415" ht="38" customHeight="1" spans="1:12">
+    <row r="415" spans="1:12" ht="38" customHeight="1">
       <c r="A415" s="4">
         <v>413</v>
       </c>
@@ -18221,7 +17604,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="416" ht="38" customHeight="1" spans="1:12">
+    <row r="416" spans="1:12" ht="38" customHeight="1">
       <c r="A416" s="4">
         <v>414</v>
       </c>
@@ -18249,7 +17632,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="417" ht="38" customHeight="1" spans="1:12">
+    <row r="417" spans="1:12" ht="38" customHeight="1">
       <c r="A417" s="4">
         <v>415</v>
       </c>
@@ -18277,7 +17660,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="418" ht="38" customHeight="1" spans="1:12">
+    <row r="418" spans="1:12" ht="38" customHeight="1">
       <c r="A418" s="4">
         <v>416</v>
       </c>
@@ -18305,7 +17688,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="419" ht="38" customHeight="1" spans="1:12">
+    <row r="419" spans="1:12" ht="38" customHeight="1">
       <c r="A419" s="4">
         <v>417</v>
       </c>
@@ -18333,7 +17716,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="420" ht="38" customHeight="1" spans="1:12">
+    <row r="420" spans="1:12" ht="38" customHeight="1">
       <c r="A420" s="4">
         <v>418</v>
       </c>
@@ -18361,7 +17744,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="421" ht="38" customHeight="1" spans="1:12">
+    <row r="421" spans="1:12" ht="38" customHeight="1">
       <c r="A421" s="4">
         <v>419</v>
       </c>
@@ -18389,7 +17772,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="422" ht="38" customHeight="1" spans="1:12">
+    <row r="422" spans="1:12" ht="38" customHeight="1">
       <c r="A422" s="4">
         <v>420</v>
       </c>
@@ -18417,7 +17800,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="423" ht="38" customHeight="1" spans="1:12">
+    <row r="423" spans="1:12" ht="38" customHeight="1">
       <c r="A423" s="4">
         <v>421</v>
       </c>
@@ -18445,7 +17828,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="424" ht="38" customHeight="1" spans="1:12">
+    <row r="424" spans="1:12" ht="38" customHeight="1">
       <c r="A424" s="4">
         <v>422</v>
       </c>
@@ -18473,7 +17856,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="425" ht="38" customHeight="1" spans="1:12">
+    <row r="425" spans="1:12" ht="38" customHeight="1">
       <c r="A425" s="4">
         <v>423</v>
       </c>
@@ -18501,7 +17884,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="426" ht="38" customHeight="1" spans="1:12">
+    <row r="426" spans="1:12" ht="38" customHeight="1">
       <c r="A426" s="4">
         <v>424</v>
       </c>
@@ -18529,7 +17912,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="427" ht="38" customHeight="1" spans="1:12">
+    <row r="427" spans="1:12" ht="38" customHeight="1">
       <c r="A427" s="4">
         <v>425</v>
       </c>
@@ -18557,7 +17940,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="428" ht="38" customHeight="1" spans="1:12">
+    <row r="428" spans="1:12" ht="38" customHeight="1">
       <c r="A428" s="4">
         <v>426</v>
       </c>
@@ -18585,7 +17968,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="429" ht="38" customHeight="1" spans="1:12">
+    <row r="429" spans="1:12" ht="38" customHeight="1">
       <c r="A429" s="4">
         <v>427</v>
       </c>
@@ -18613,7 +17996,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="430" ht="38" customHeight="1" spans="1:12">
+    <row r="430" spans="1:12" ht="38" customHeight="1">
       <c r="A430" s="4">
         <v>428</v>
       </c>
@@ -18641,7 +18024,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="431" ht="38" customHeight="1" spans="1:12">
+    <row r="431" spans="1:12" ht="38" customHeight="1">
       <c r="A431" s="4">
         <v>429</v>
       </c>
@@ -18669,7 +18052,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="432" ht="38" customHeight="1" spans="1:12">
+    <row r="432" spans="1:12" ht="38" customHeight="1">
       <c r="A432" s="4">
         <v>430</v>
       </c>
@@ -18697,7 +18080,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="433" ht="38" customHeight="1" spans="1:12">
+    <row r="433" spans="1:12" ht="38" customHeight="1">
       <c r="A433" s="4">
         <v>431</v>
       </c>
@@ -18725,7 +18108,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="434" ht="38" customHeight="1" spans="1:12">
+    <row r="434" spans="1:12" ht="38" customHeight="1">
       <c r="A434" s="4">
         <v>432</v>
       </c>
@@ -18753,7 +18136,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="435" ht="38" customHeight="1" spans="1:12">
+    <row r="435" spans="1:12" ht="38" customHeight="1">
       <c r="A435" s="4">
         <v>433</v>
       </c>
@@ -18781,7 +18164,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="436" ht="38" customHeight="1" spans="1:12">
+    <row r="436" spans="1:12" ht="38" customHeight="1">
       <c r="A436" s="4">
         <v>434</v>
       </c>
@@ -18809,7 +18192,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="437" ht="38" customHeight="1" spans="1:12">
+    <row r="437" spans="1:12" ht="38" customHeight="1">
       <c r="A437" s="4">
         <v>435</v>
       </c>
@@ -18837,7 +18220,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="438" ht="38" customHeight="1" spans="1:12">
+    <row r="438" spans="1:12" ht="38" customHeight="1">
       <c r="A438" s="4">
         <v>436</v>
       </c>
@@ -18865,7 +18248,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="439" ht="38" customHeight="1" spans="1:12">
+    <row r="439" spans="1:12" ht="38" customHeight="1">
       <c r="A439" s="4">
         <v>437</v>
       </c>
@@ -18893,7 +18276,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="440" ht="38" customHeight="1" spans="1:12">
+    <row r="440" spans="1:12" ht="38" customHeight="1">
       <c r="A440" s="4">
         <v>438</v>
       </c>
@@ -18921,7 +18304,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="441" ht="38" customHeight="1" spans="1:12">
+    <row r="441" spans="1:12" ht="38" customHeight="1">
       <c r="A441" s="4">
         <v>439</v>
       </c>
@@ -18949,7 +18332,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="442" ht="38" customHeight="1" spans="1:12">
+    <row r="442" spans="1:12" ht="38" customHeight="1">
       <c r="A442" s="4">
         <v>440</v>
       </c>
@@ -18977,7 +18360,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="443" ht="38" customHeight="1" spans="1:12">
+    <row r="443" spans="1:12" ht="38" customHeight="1">
       <c r="A443" s="4">
         <v>441</v>
       </c>
@@ -19005,7 +18388,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="444" ht="38" customHeight="1" spans="1:12">
+    <row r="444" spans="1:12" ht="38" customHeight="1">
       <c r="A444" s="4">
         <v>442</v>
       </c>
@@ -19033,7 +18416,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="445" ht="38" customHeight="1" spans="1:12">
+    <row r="445" spans="1:12" ht="38" customHeight="1">
       <c r="A445" s="4">
         <v>443</v>
       </c>
@@ -19061,7 +18444,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="446" ht="38" customHeight="1" spans="1:12">
+    <row r="446" spans="1:12" ht="38" customHeight="1">
       <c r="A446" s="4">
         <v>444</v>
       </c>
@@ -19089,7 +18472,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="447" ht="38" customHeight="1" spans="1:12">
+    <row r="447" spans="1:12" ht="38" customHeight="1">
       <c r="A447" s="4">
         <v>445</v>
       </c>
@@ -19117,7 +18500,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="448" ht="38" customHeight="1" spans="1:12">
+    <row r="448" spans="1:12" ht="38" customHeight="1">
       <c r="A448" s="4">
         <v>446</v>
       </c>
@@ -19145,7 +18528,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="449" ht="38" customHeight="1" spans="1:12">
+    <row r="449" spans="1:12" ht="38" customHeight="1">
       <c r="A449" s="4">
         <v>447</v>
       </c>
@@ -19173,7 +18556,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="450" ht="38" customHeight="1" spans="1:12">
+    <row r="450" spans="1:12" ht="38" customHeight="1">
       <c r="A450" s="4">
         <v>448</v>
       </c>
@@ -19201,7 +18584,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="451" ht="38" customHeight="1" spans="1:12">
+    <row r="451" spans="1:12" ht="38" customHeight="1">
       <c r="A451" s="4">
         <v>449</v>
       </c>
@@ -19229,7 +18612,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="452" ht="38" customHeight="1" spans="1:12">
+    <row r="452" spans="1:12" ht="38" customHeight="1">
       <c r="A452" s="4">
         <v>450</v>
       </c>
@@ -19257,7 +18640,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="453" ht="38" customHeight="1" spans="1:12">
+    <row r="453" spans="1:12" ht="38" customHeight="1">
       <c r="A453" s="4">
         <v>451</v>
       </c>
@@ -19285,7 +18668,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="454" ht="38" customHeight="1" spans="1:12">
+    <row r="454" spans="1:12" ht="38" customHeight="1">
       <c r="A454" s="4">
         <v>452</v>
       </c>
@@ -19313,7 +18696,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="455" ht="38" customHeight="1" spans="1:12">
+    <row r="455" spans="1:12" ht="38" customHeight="1">
       <c r="A455" s="4">
         <v>453</v>
       </c>
@@ -19341,7 +18724,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="456" ht="38" customHeight="1" spans="1:12">
+    <row r="456" spans="1:12" ht="38" customHeight="1">
       <c r="A456" s="4">
         <v>454</v>
       </c>
@@ -19369,7 +18752,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="457" ht="38" customHeight="1" spans="1:12">
+    <row r="457" spans="1:12" ht="38" customHeight="1">
       <c r="A457" s="4">
         <v>455</v>
       </c>
@@ -19397,7 +18780,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="458" ht="38" customHeight="1" spans="1:12">
+    <row r="458" spans="1:12" ht="38" customHeight="1">
       <c r="A458" s="4">
         <v>456</v>
       </c>
@@ -19425,7 +18808,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="459" ht="38" customHeight="1" spans="1:12">
+    <row r="459" spans="1:12" ht="38" customHeight="1">
       <c r="A459" s="4">
         <v>457</v>
       </c>
@@ -19453,7 +18836,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="460" ht="38" customHeight="1" spans="1:12">
+    <row r="460" spans="1:12" ht="38" customHeight="1">
       <c r="A460" s="4">
         <v>458</v>
       </c>
@@ -19481,7 +18864,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="461" ht="38" customHeight="1" spans="1:12">
+    <row r="461" spans="1:12" ht="38" customHeight="1">
       <c r="A461" s="4">
         <v>459</v>
       </c>
@@ -19509,7 +18892,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="462" ht="38" customHeight="1" spans="1:12">
+    <row r="462" spans="1:12" ht="38" customHeight="1">
       <c r="A462" s="4">
         <v>460</v>
       </c>
@@ -19537,7 +18920,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="463" ht="38" customHeight="1" spans="1:12">
+    <row r="463" spans="1:12" ht="38" customHeight="1">
       <c r="A463" s="4">
         <v>461</v>
       </c>
@@ -19565,7 +18948,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="464" ht="38" customHeight="1" spans="1:12">
+    <row r="464" spans="1:12" ht="38" customHeight="1">
       <c r="A464" s="4">
         <v>462</v>
       </c>
@@ -19593,7 +18976,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="465" ht="38" customHeight="1" spans="1:12">
+    <row r="465" spans="1:12" ht="38" customHeight="1">
       <c r="A465" s="4">
         <v>463</v>
       </c>
@@ -19621,7 +19004,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="466" ht="38" customHeight="1" spans="1:12">
+    <row r="466" spans="1:12" ht="38" customHeight="1">
       <c r="A466" s="4">
         <v>464</v>
       </c>
@@ -19649,7 +19032,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="467" ht="38" customHeight="1" spans="1:12">
+    <row r="467" spans="1:12" ht="38" customHeight="1">
       <c r="A467" s="4">
         <v>465</v>
       </c>
@@ -19677,7 +19060,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="468" ht="38" customHeight="1" spans="1:12">
+    <row r="468" spans="1:12" ht="38" customHeight="1">
       <c r="A468" s="4">
         <v>466</v>
       </c>
@@ -19705,7 +19088,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="469" ht="38" customHeight="1" spans="1:12">
+    <row r="469" spans="1:12" ht="38" customHeight="1">
       <c r="A469" s="4">
         <v>467</v>
       </c>
@@ -19733,7 +19116,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="470" ht="38" customHeight="1" spans="1:12">
+    <row r="470" spans="1:12" ht="38" customHeight="1">
       <c r="A470" s="4">
         <v>468</v>
       </c>
@@ -19761,7 +19144,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="471" ht="38" customHeight="1" spans="1:12">
+    <row r="471" spans="1:12" ht="38" customHeight="1">
       <c r="A471" s="4">
         <v>469</v>
       </c>
@@ -19789,7 +19172,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="472" ht="38" customHeight="1" spans="1:12">
+    <row r="472" spans="1:12" ht="38" customHeight="1">
       <c r="A472" s="4">
         <v>470</v>
       </c>
@@ -19817,7 +19200,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="473" ht="38" customHeight="1" spans="1:12">
+    <row r="473" spans="1:12" ht="38" customHeight="1">
       <c r="A473" s="4">
         <v>471</v>
       </c>
@@ -19845,7 +19228,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="474" ht="38" customHeight="1" spans="1:12">
+    <row r="474" spans="1:12" ht="38" customHeight="1">
       <c r="A474" s="4">
         <v>472</v>
       </c>
@@ -19873,7 +19256,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="475" ht="38" customHeight="1" spans="1:12">
+    <row r="475" spans="1:12" ht="38" customHeight="1">
       <c r="A475" s="4">
         <v>473</v>
       </c>
@@ -19901,7 +19284,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="476" ht="38" customHeight="1" spans="1:12">
+    <row r="476" spans="1:12" ht="38" customHeight="1">
       <c r="A476" s="4">
         <v>474</v>
       </c>
@@ -19929,7 +19312,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="477" ht="38" customHeight="1" spans="1:12">
+    <row r="477" spans="1:12" ht="38" customHeight="1">
       <c r="A477" s="4">
         <v>475</v>
       </c>
@@ -19957,7 +19340,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="478" ht="38" customHeight="1" spans="1:12">
+    <row r="478" spans="1:12" ht="38" customHeight="1">
       <c r="A478" s="4">
         <v>476</v>
       </c>
@@ -19985,7 +19368,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="479" ht="38" customHeight="1" spans="1:12">
+    <row r="479" spans="1:12" ht="38" customHeight="1">
       <c r="A479" s="4">
         <v>477</v>
       </c>
@@ -20013,7 +19396,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="480" ht="38" customHeight="1" spans="1:12">
+    <row r="480" spans="1:12" ht="38" customHeight="1">
       <c r="A480" s="4">
         <v>478</v>
       </c>
@@ -20041,7 +19424,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="481" ht="38" customHeight="1" spans="1:12">
+    <row r="481" spans="1:12" ht="38" customHeight="1">
       <c r="A481" s="4">
         <v>479</v>
       </c>
@@ -20069,7 +19452,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="482" ht="38" customHeight="1" spans="1:12">
+    <row r="482" spans="1:12" ht="38" customHeight="1">
       <c r="A482" s="4">
         <v>480</v>
       </c>
@@ -20097,7 +19480,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="483" ht="38" customHeight="1" spans="1:12">
+    <row r="483" spans="1:12" ht="38" customHeight="1">
       <c r="A483" s="4">
         <v>481</v>
       </c>
@@ -20125,7 +19508,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="484" ht="38" customHeight="1" spans="1:12">
+    <row r="484" spans="1:12" ht="38" customHeight="1">
       <c r="A484" s="4">
         <v>482</v>
       </c>
@@ -20153,7 +19536,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="485" ht="38" customHeight="1" spans="1:12">
+    <row r="485" spans="1:12" ht="38" customHeight="1">
       <c r="A485" s="4">
         <v>483</v>
       </c>
@@ -20181,7 +19564,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="486" ht="38" customHeight="1" spans="1:12">
+    <row r="486" spans="1:12" ht="38" customHeight="1">
       <c r="A486" s="4">
         <v>484</v>
       </c>
@@ -20209,7 +19592,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="487" ht="38" customHeight="1" spans="1:12">
+    <row r="487" spans="1:12" ht="38" customHeight="1">
       <c r="A487" s="4">
         <v>485</v>
       </c>
@@ -20237,7 +19620,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="488" ht="38" customHeight="1" spans="1:12">
+    <row r="488" spans="1:12" ht="38" customHeight="1">
       <c r="A488" s="4">
         <v>486</v>
       </c>
@@ -20265,7 +19648,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="489" ht="38" customHeight="1" spans="1:12">
+    <row r="489" spans="1:12" ht="38" customHeight="1">
       <c r="A489" s="4">
         <v>487</v>
       </c>
@@ -20293,7 +19676,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="490" ht="38" customHeight="1" spans="1:12">
+    <row r="490" spans="1:12" ht="38" customHeight="1">
       <c r="A490" s="4">
         <v>488</v>
       </c>
@@ -20321,7 +19704,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="491" ht="38" customHeight="1" spans="1:12">
+    <row r="491" spans="1:12" ht="38" customHeight="1">
       <c r="A491" s="4">
         <v>489</v>
       </c>
@@ -20349,7 +19732,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="492" ht="38" customHeight="1" spans="1:12">
+    <row r="492" spans="1:12" ht="38" customHeight="1">
       <c r="A492" s="4">
         <v>490</v>
       </c>
@@ -20377,7 +19760,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="493" ht="38" customHeight="1" spans="1:12">
+    <row r="493" spans="1:12" ht="38" customHeight="1">
       <c r="A493" s="4">
         <v>491</v>
       </c>
@@ -20405,7 +19788,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="494" ht="38" customHeight="1" spans="1:12">
+    <row r="494" spans="1:12" ht="38" customHeight="1">
       <c r="A494" s="4">
         <v>492</v>
       </c>
@@ -20433,7 +19816,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="495" ht="38" customHeight="1" spans="1:12">
+    <row r="495" spans="1:12" ht="38" customHeight="1">
       <c r="A495" s="4">
         <v>493</v>
       </c>
@@ -20461,7 +19844,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="496" ht="38" customHeight="1" spans="1:12">
+    <row r="496" spans="1:12" ht="38" customHeight="1">
       <c r="A496" s="4">
         <v>494</v>
       </c>
@@ -20489,7 +19872,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="497" ht="38" customHeight="1" spans="1:12">
+    <row r="497" spans="1:12" ht="38" customHeight="1">
       <c r="A497" s="4">
         <v>495</v>
       </c>
@@ -20517,7 +19900,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="498" ht="38" customHeight="1" spans="1:12">
+    <row r="498" spans="1:12" ht="38" customHeight="1">
       <c r="A498" s="4">
         <v>496</v>
       </c>
@@ -20545,7 +19928,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="499" ht="38" customHeight="1" spans="1:12">
+    <row r="499" spans="1:12" ht="38" customHeight="1">
       <c r="A499" s="4">
         <v>497</v>
       </c>
@@ -20573,7 +19956,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="500" ht="38" customHeight="1" spans="1:12">
+    <row r="500" spans="1:12" ht="38" customHeight="1">
       <c r="A500" s="4">
         <v>498</v>
       </c>
@@ -20601,7 +19984,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="501" ht="38" customHeight="1" spans="1:12">
+    <row r="501" spans="1:12" ht="38" customHeight="1">
       <c r="A501" s="4">
         <v>499</v>
       </c>
@@ -20629,7 +20012,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="502" ht="38" customHeight="1" spans="1:12">
+    <row r="502" spans="1:12" ht="38" customHeight="1">
       <c r="A502" s="4">
         <v>500</v>
       </c>
@@ -20657,7 +20040,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="503" ht="38" customHeight="1" spans="1:12">
+    <row r="503" spans="1:12" ht="38" customHeight="1">
       <c r="A503" s="4">
         <v>501</v>
       </c>
@@ -20685,7 +20068,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="504" ht="38" customHeight="1" spans="1:12">
+    <row r="504" spans="1:12" ht="38" customHeight="1">
       <c r="A504" s="4">
         <v>502</v>
       </c>
@@ -20713,7 +20096,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="505" ht="38" customHeight="1" spans="1:12">
+    <row r="505" spans="1:12" ht="38" customHeight="1">
       <c r="A505" s="4">
         <v>503</v>
       </c>
@@ -20741,7 +20124,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="506" ht="38" customHeight="1" spans="1:12">
+    <row r="506" spans="1:12" ht="38" customHeight="1">
       <c r="A506" s="4">
         <v>504</v>
       </c>
@@ -20769,7 +20152,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="507" ht="38" customHeight="1" spans="1:12">
+    <row r="507" spans="1:12" ht="38" customHeight="1">
       <c r="A507" s="4">
         <v>505</v>
       </c>
@@ -20797,7 +20180,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="508" ht="38" customHeight="1" spans="1:12">
+    <row r="508" spans="1:12" ht="38" customHeight="1">
       <c r="A508" s="4">
         <v>506</v>
       </c>
@@ -20825,7 +20208,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="509" ht="38" customHeight="1" spans="1:12">
+    <row r="509" spans="1:12" ht="38" customHeight="1">
       <c r="A509" s="4">
         <v>507</v>
       </c>
@@ -20853,7 +20236,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="510" ht="38" customHeight="1" spans="1:12">
+    <row r="510" spans="1:12" ht="38" customHeight="1">
       <c r="A510" s="4">
         <v>508</v>
       </c>
@@ -20881,7 +20264,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="511" ht="38" customHeight="1" spans="1:12">
+    <row r="511" spans="1:12" ht="38" customHeight="1">
       <c r="A511" s="4">
         <v>509</v>
       </c>
@@ -20909,7 +20292,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="512" ht="38" customHeight="1" spans="1:12">
+    <row r="512" spans="1:12" ht="38" customHeight="1">
       <c r="A512" s="4">
         <v>510</v>
       </c>
@@ -20937,7 +20320,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="513" ht="38" customHeight="1" spans="1:12">
+    <row r="513" spans="1:12" ht="38" customHeight="1">
       <c r="A513" s="4">
         <v>511</v>
       </c>
@@ -20965,7 +20348,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="514" ht="38" customHeight="1" spans="1:12">
+    <row r="514" spans="1:12" ht="38" customHeight="1">
       <c r="A514" s="4">
         <v>512</v>
       </c>
@@ -20993,7 +20376,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="515" ht="38" customHeight="1" spans="1:12">
+    <row r="515" spans="1:12" ht="38" customHeight="1">
       <c r="A515" s="4">
         <v>513</v>
       </c>
@@ -21021,7 +20404,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="516" ht="38" customHeight="1" spans="1:12">
+    <row r="516" spans="1:12" ht="38" customHeight="1">
       <c r="A516" s="4">
         <v>514</v>
       </c>
@@ -21049,7 +20432,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="517" ht="38" customHeight="1" spans="1:12">
+    <row r="517" spans="1:12" ht="38" customHeight="1">
       <c r="A517" s="4">
         <v>515</v>
       </c>
@@ -21077,7 +20460,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="518" ht="38" customHeight="1" spans="1:12">
+    <row r="518" spans="1:12" ht="38" customHeight="1">
       <c r="A518" s="4">
         <v>516</v>
       </c>
@@ -21105,7 +20488,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="519" ht="38" customHeight="1" spans="1:12">
+    <row r="519" spans="1:12" ht="38" customHeight="1">
       <c r="A519" s="4">
         <v>517</v>
       </c>
@@ -21133,7 +20516,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="520" ht="38" customHeight="1" spans="1:12">
+    <row r="520" spans="1:12" ht="38" customHeight="1">
       <c r="A520" s="4">
         <v>518</v>
       </c>
@@ -21161,7 +20544,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="521" ht="38" customHeight="1" spans="1:12">
+    <row r="521" spans="1:12" ht="38" customHeight="1">
       <c r="A521" s="4">
         <v>519</v>
       </c>
@@ -21189,7 +20572,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="522" ht="38" customHeight="1" spans="1:12">
+    <row r="522" spans="1:12" ht="38" customHeight="1">
       <c r="A522" s="4">
         <v>520</v>
       </c>
@@ -21217,7 +20600,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="523" ht="38" customHeight="1" spans="1:12">
+    <row r="523" spans="1:12" ht="38" customHeight="1">
       <c r="A523" s="4">
         <v>521</v>
       </c>
@@ -21245,7 +20628,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="524" ht="38" customHeight="1" spans="1:12">
+    <row r="524" spans="1:12" ht="38" customHeight="1">
       <c r="A524" s="4">
         <v>522</v>
       </c>
@@ -21273,7 +20656,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="525" ht="38" customHeight="1" spans="1:12">
+    <row r="525" spans="1:12" ht="38" customHeight="1">
       <c r="A525" s="4">
         <v>523</v>
       </c>
@@ -21301,7 +20684,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="526" ht="38" customHeight="1" spans="1:12">
+    <row r="526" spans="1:12" ht="38" customHeight="1">
       <c r="A526" s="4">
         <v>524</v>
       </c>
@@ -21329,7 +20712,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="527" ht="38" customHeight="1" spans="1:12">
+    <row r="527" spans="1:12" ht="38" customHeight="1">
       <c r="A527" s="4">
         <v>525</v>
       </c>
@@ -21357,7 +20740,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="528" ht="38" customHeight="1" spans="1:12">
+    <row r="528" spans="1:12" ht="38" customHeight="1">
       <c r="A528" s="4">
         <v>526</v>
       </c>
@@ -21385,7 +20768,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="529" ht="38" customHeight="1" spans="1:12">
+    <row r="529" spans="1:12" ht="38" customHeight="1">
       <c r="A529" s="4">
         <v>527</v>
       </c>
@@ -21413,7 +20796,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="530" ht="38" customHeight="1" spans="1:12">
+    <row r="530" spans="1:12" ht="38" customHeight="1">
       <c r="A530" s="4">
         <v>528</v>
       </c>
@@ -21441,7 +20824,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="531" ht="38" customHeight="1" spans="1:12">
+    <row r="531" spans="1:12" ht="38" customHeight="1">
       <c r="A531" s="4">
         <v>529</v>
       </c>
@@ -21469,7 +20852,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="532" ht="38" customHeight="1" spans="1:12">
+    <row r="532" spans="1:12" ht="38" customHeight="1">
       <c r="A532" s="4">
         <v>530</v>
       </c>
@@ -21497,7 +20880,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="533" ht="38" customHeight="1" spans="1:12">
+    <row r="533" spans="1:12" ht="38" customHeight="1">
       <c r="A533" s="4">
         <v>531</v>
       </c>
@@ -21525,7 +20908,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="534" ht="38" customHeight="1" spans="1:12">
+    <row r="534" spans="1:12" ht="38" customHeight="1">
       <c r="A534" s="4">
         <v>532</v>
       </c>
@@ -21553,7 +20936,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="535" ht="38" customHeight="1" spans="1:12">
+    <row r="535" spans="1:12" ht="38" customHeight="1">
       <c r="A535" s="4">
         <v>533</v>
       </c>
@@ -21581,7 +20964,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="536" ht="38" customHeight="1" spans="1:12">
+    <row r="536" spans="1:12" ht="38" customHeight="1">
       <c r="A536" s="4">
         <v>534</v>
       </c>
@@ -21609,7 +20992,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="537" ht="38" customHeight="1" spans="1:12">
+    <row r="537" spans="1:12" ht="38" customHeight="1">
       <c r="A537" s="4">
         <v>535</v>
       </c>
@@ -21637,7 +21020,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="538" ht="38" customHeight="1" spans="1:12">
+    <row r="538" spans="1:12" ht="38" customHeight="1">
       <c r="A538" s="4">
         <v>536</v>
       </c>
@@ -21665,7 +21048,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="539" ht="38" customHeight="1" spans="1:12">
+    <row r="539" spans="1:12" ht="38" customHeight="1">
       <c r="A539" s="4">
         <v>537</v>
       </c>
@@ -21693,7 +21076,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="540" ht="38" customHeight="1" spans="1:12">
+    <row r="540" spans="1:12" ht="38" customHeight="1">
       <c r="A540" s="4">
         <v>538</v>
       </c>
@@ -21721,7 +21104,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="541" ht="38" customHeight="1" spans="1:12">
+    <row r="541" spans="1:12" ht="38" customHeight="1">
       <c r="A541" s="4">
         <v>539</v>
       </c>
@@ -21749,7 +21132,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="542" ht="38" customHeight="1" spans="1:12">
+    <row r="542" spans="1:12" ht="38" customHeight="1">
       <c r="A542" s="4">
         <v>540</v>
       </c>
@@ -21765,1055 +21148,1055 @@
       <c r="K542" s="4"/>
       <c r="L542" s="4"/>
     </row>
-    <row r="543" ht="38" customHeight="1" spans="1:12">
+    <row r="543" spans="1:12" ht="38" customHeight="1">
       <c r="A543" s="4">
         <v>541</v>
       </c>
-      <c r="B543" s="5" t="s">
+      <c r="B543" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="C543" s="5" t="s">
+      <c r="C543" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="D543" s="5" t="s">
+      <c r="D543" s="1" t="s">
         <v>1427</v>
       </c>
       <c r="E543" s="4" t="s">
         <v>1428</v>
       </c>
-      <c r="F543" s="5" t="s">
+      <c r="F543" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G543" s="5"/>
-      <c r="H543" s="5"/>
-      <c r="I543" s="5"/>
-      <c r="J543" s="5"/>
-      <c r="K543" s="5"/>
-      <c r="L543" s="6" t="str">
+      <c r="G543" s="1"/>
+      <c r="H543" s="1"/>
+      <c r="I543" s="1"/>
+      <c r="J543" s="1"/>
+      <c r="K543" s="1"/>
+      <c r="L543" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_4B2214014A4B4B48ACC679172BEDBD5E",1)</f>
         <v>=DISPIMG("ID_4B2214014A4B4B48ACC679172BEDBD5E",1)</v>
       </c>
     </row>
-    <row r="544" ht="38" customHeight="1" spans="1:12">
+    <row r="544" spans="1:12" ht="38" customHeight="1">
       <c r="A544" s="4">
         <v>542</v>
       </c>
-      <c r="B544" s="5" t="s">
+      <c r="B544" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="C544" s="5" t="s">
+      <c r="C544" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="D544" s="5" t="s">
+      <c r="D544" s="1" t="s">
         <v>1427</v>
       </c>
       <c r="E544" s="4" t="s">
         <v>1428</v>
       </c>
-      <c r="F544" s="5" t="s">
+      <c r="F544" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G544" s="5"/>
-      <c r="H544" s="5"/>
-      <c r="I544" s="5"/>
-      <c r="J544" s="5"/>
-      <c r="K544" s="5"/>
-      <c r="L544" s="6" t="str">
+      <c r="G544" s="1"/>
+      <c r="H544" s="1"/>
+      <c r="I544" s="1"/>
+      <c r="J544" s="1"/>
+      <c r="K544" s="1"/>
+      <c r="L544" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_C315B3116B164F789857F0B4AC25C7F9",1)</f>
         <v>=DISPIMG("ID_C315B3116B164F789857F0B4AC25C7F9",1)</v>
       </c>
     </row>
-    <row r="545" ht="38" customHeight="1" spans="1:12">
+    <row r="545" spans="1:12" ht="38" customHeight="1">
       <c r="A545" s="4">
         <v>543</v>
       </c>
-      <c r="B545" s="5" t="s">
+      <c r="B545" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="C545" s="5" t="s">
+      <c r="C545" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="D545" s="5" t="s">
+      <c r="D545" s="1" t="s">
         <v>1427</v>
       </c>
       <c r="E545" s="4" t="s">
         <v>1432</v>
       </c>
-      <c r="F545" s="5" t="s">
+      <c r="F545" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G545" s="5"/>
-      <c r="H545" s="5"/>
-      <c r="I545" s="5"/>
-      <c r="J545" s="5"/>
-      <c r="K545" s="5"/>
-      <c r="L545" s="6" t="str">
+      <c r="G545" s="1"/>
+      <c r="H545" s="1"/>
+      <c r="I545" s="1"/>
+      <c r="J545" s="1"/>
+      <c r="K545" s="1"/>
+      <c r="L545" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_C315B3116B164F789857F0B4AC25C7F9",1)</f>
         <v>=DISPIMG("ID_C315B3116B164F789857F0B4AC25C7F9",1)</v>
       </c>
     </row>
-    <row r="546" ht="38" customHeight="1" spans="1:12">
+    <row r="546" spans="1:12" ht="38" customHeight="1">
       <c r="A546" s="4">
         <v>544</v>
       </c>
-      <c r="B546" s="5" t="s">
+      <c r="B546" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C546" s="5" t="s">
+      <c r="C546" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="D546" s="5" t="s">
+      <c r="D546" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E546" s="4" t="s">
         <v>1434</v>
       </c>
-      <c r="F546" s="5" t="s">
+      <c r="F546" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G546" s="5"/>
-      <c r="H546" s="5"/>
-      <c r="I546" s="5"/>
-      <c r="J546" s="5"/>
-      <c r="K546" s="5"/>
-      <c r="L546" s="6" t="str">
+      <c r="G546" s="1"/>
+      <c r="H546" s="1"/>
+      <c r="I546" s="1"/>
+      <c r="J546" s="1"/>
+      <c r="K546" s="1"/>
+      <c r="L546" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B12D9660C492480C8334C7789BDDE2B9",1)</f>
         <v>=DISPIMG("ID_B12D9660C492480C8334C7789BDDE2B9",1)</v>
       </c>
     </row>
-    <row r="547" ht="38" customHeight="1" spans="1:12">
+    <row r="547" spans="1:12" ht="38" customHeight="1">
       <c r="A547" s="4">
         <v>545</v>
       </c>
-      <c r="B547" s="5" t="s">
+      <c r="B547" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C547" s="5" t="s">
+      <c r="C547" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="D547" s="5" t="s">
+      <c r="D547" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E547" s="4"/>
-      <c r="F547" s="5" t="s">
+      <c r="F547" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G547" s="5"/>
-      <c r="H547" s="5"/>
-      <c r="I547" s="5"/>
-      <c r="J547" s="5"/>
-      <c r="K547" s="5"/>
-      <c r="L547" s="6" t="str">
+      <c r="G547" s="1"/>
+      <c r="H547" s="1"/>
+      <c r="I547" s="1"/>
+      <c r="J547" s="1"/>
+      <c r="K547" s="1"/>
+      <c r="L547" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D046CFFC483F4109B003886F305674C7",1)</f>
         <v>=DISPIMG("ID_D046CFFC483F4109B003886F305674C7",1)</v>
       </c>
     </row>
-    <row r="548" ht="38" customHeight="1" spans="1:12">
+    <row r="548" spans="1:12" ht="38" customHeight="1">
       <c r="A548" s="4">
         <v>546</v>
       </c>
-      <c r="B548" s="5" t="s">
+      <c r="B548" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C548" s="5" t="s">
+      <c r="C548" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="D548" s="5" t="s">
+      <c r="D548" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E548" s="4"/>
-      <c r="F548" s="5" t="s">
+      <c r="F548" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G548" s="5"/>
-      <c r="H548" s="5"/>
-      <c r="I548" s="5"/>
-      <c r="J548" s="5"/>
-      <c r="K548" s="5"/>
-      <c r="L548" s="6" t="str">
+      <c r="G548" s="1"/>
+      <c r="H548" s="1"/>
+      <c r="I548" s="1"/>
+      <c r="J548" s="1"/>
+      <c r="K548" s="1"/>
+      <c r="L548" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_5B5A17EB0FF043D38E64C8F82E025C62",1)</f>
         <v>=DISPIMG("ID_5B5A17EB0FF043D38E64C8F82E025C62",1)</v>
       </c>
     </row>
-    <row r="549" ht="38" customHeight="1" spans="1:12">
+    <row r="549" spans="1:12" ht="38" customHeight="1">
       <c r="A549" s="4">
         <v>547</v>
       </c>
-      <c r="B549" s="5" t="s">
+      <c r="B549" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C549" s="5" t="s">
+      <c r="C549" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="D549" s="5" t="s">
+      <c r="D549" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E549" s="4"/>
-      <c r="F549" s="5" t="s">
+      <c r="F549" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G549" s="5"/>
-      <c r="H549" s="5"/>
-      <c r="I549" s="5"/>
-      <c r="J549" s="5"/>
-      <c r="K549" s="5"/>
-      <c r="L549" s="6" t="str">
+      <c r="G549" s="1"/>
+      <c r="H549" s="1"/>
+      <c r="I549" s="1"/>
+      <c r="J549" s="1"/>
+      <c r="K549" s="1"/>
+      <c r="L549" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_9202E7D7ACB54153A2B51B81C27F337D",1)</f>
         <v>=DISPIMG("ID_9202E7D7ACB54153A2B51B81C27F337D",1)</v>
       </c>
     </row>
-    <row r="550" ht="38" customHeight="1" spans="1:12">
+    <row r="550" spans="1:12" ht="38" customHeight="1">
       <c r="A550" s="4">
         <v>548</v>
       </c>
-      <c r="B550" s="5" t="s">
+      <c r="B550" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C550" s="5" t="s">
+      <c r="C550" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="D550" s="5" t="s">
+      <c r="D550" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E550" s="4"/>
-      <c r="F550" s="5" t="s">
+      <c r="F550" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G550" s="5"/>
-      <c r="H550" s="5"/>
-      <c r="I550" s="5"/>
-      <c r="J550" s="5"/>
-      <c r="K550" s="5"/>
-      <c r="L550" s="6" t="str">
+      <c r="G550" s="1"/>
+      <c r="H550" s="1"/>
+      <c r="I550" s="1"/>
+      <c r="J550" s="1"/>
+      <c r="K550" s="1"/>
+      <c r="L550" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B659BEF694934FEE9287923DC5DE4728",1)</f>
         <v>=DISPIMG("ID_B659BEF694934FEE9287923DC5DE4728",1)</v>
       </c>
     </row>
-    <row r="551" ht="38" customHeight="1" spans="1:12">
+    <row r="551" spans="1:12" ht="38" customHeight="1">
       <c r="A551" s="4">
         <v>549</v>
       </c>
-      <c r="B551" s="5" t="s">
+      <c r="B551" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="C551" s="5" t="s">
+      <c r="C551" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="D551" s="5" t="s">
+      <c r="D551" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E551" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="F551" s="5"/>
-      <c r="G551" s="5"/>
-      <c r="H551" s="5"/>
-      <c r="I551" s="5"/>
-      <c r="J551" s="5"/>
-      <c r="K551" s="5"/>
-      <c r="L551" s="6" t="str">
+      <c r="F551" s="1"/>
+      <c r="G551" s="1"/>
+      <c r="H551" s="1"/>
+      <c r="I551" s="1"/>
+      <c r="J551" s="1"/>
+      <c r="K551" s="1"/>
+      <c r="L551" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_78465C75452048F98CE7EF2BA9DA4733",1)</f>
         <v>=DISPIMG("ID_78465C75452048F98CE7EF2BA9DA4733",1)</v>
       </c>
     </row>
-    <row r="552" ht="38" customHeight="1" spans="1:12">
+    <row r="552" spans="1:12" ht="38" customHeight="1">
       <c r="A552" s="4">
         <v>550</v>
       </c>
-      <c r="B552" s="5" t="s">
+      <c r="B552" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="C552" s="5" t="s">
+      <c r="C552" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="D552" s="5" t="s">
+      <c r="D552" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E552" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="F552" s="5"/>
-      <c r="G552" s="5"/>
-      <c r="H552" s="5"/>
-      <c r="I552" s="5"/>
-      <c r="J552" s="5"/>
-      <c r="K552" s="5"/>
-      <c r="L552" s="6" t="str">
+      <c r="F552" s="1"/>
+      <c r="G552" s="1"/>
+      <c r="H552" s="1"/>
+      <c r="I552" s="1"/>
+      <c r="J552" s="1"/>
+      <c r="K552" s="1"/>
+      <c r="L552" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_6E7E50447B154886B145FA9DAFF45441",1)</f>
         <v>=DISPIMG("ID_6E7E50447B154886B145FA9DAFF45441",1)</v>
       </c>
     </row>
-    <row r="553" ht="38" customHeight="1" spans="1:12">
+    <row r="553" spans="1:12" ht="38" customHeight="1">
       <c r="A553" s="4">
         <v>551</v>
       </c>
-      <c r="B553" s="5" t="s">
+      <c r="B553" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="C553" s="5" t="s">
+      <c r="C553" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="D553" s="5" t="s">
+      <c r="D553" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E553" s="4" t="s">
         <v>1445</v>
       </c>
-      <c r="F553" s="5" t="s">
+      <c r="F553" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="G553" s="5"/>
-      <c r="H553" s="5"/>
-      <c r="I553" s="5"/>
-      <c r="J553" s="5"/>
-      <c r="K553" s="5"/>
-      <c r="L553" s="6" t="str">
+      <c r="G553" s="1"/>
+      <c r="H553" s="1"/>
+      <c r="I553" s="1"/>
+      <c r="J553" s="1"/>
+      <c r="K553" s="1"/>
+      <c r="L553" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_941AB3DA75734C1EBB0BEDFA29BBBF1C",1)</f>
         <v>=DISPIMG("ID_941AB3DA75734C1EBB0BEDFA29BBBF1C",1)</v>
       </c>
     </row>
-    <row r="554" ht="38" customHeight="1" spans="1:12">
+    <row r="554" spans="1:12" ht="38" customHeight="1">
       <c r="A554" s="4">
         <v>552</v>
       </c>
-      <c r="B554" s="5" t="s">
+      <c r="B554" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C554" s="5" t="s">
+      <c r="C554" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="D554" s="5" t="s">
+      <c r="D554" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E554" s="4" t="s">
         <v>1448</v>
       </c>
-      <c r="F554" s="5"/>
-      <c r="G554" s="5"/>
-      <c r="H554" s="5"/>
-      <c r="I554" s="5"/>
-      <c r="J554" s="5"/>
-      <c r="K554" s="5"/>
-      <c r="L554" s="6" t="str">
+      <c r="F554" s="1"/>
+      <c r="G554" s="1"/>
+      <c r="H554" s="1"/>
+      <c r="I554" s="1"/>
+      <c r="J554" s="1"/>
+      <c r="K554" s="1"/>
+      <c r="L554" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_864BCF6B2B5649C18701BD2E8E17B3CF",1)</f>
         <v>=DISPIMG("ID_864BCF6B2B5649C18701BD2E8E17B3CF",1)</v>
       </c>
     </row>
-    <row r="555" ht="38" customHeight="1" spans="1:12">
+    <row r="555" spans="1:12" ht="38" customHeight="1">
       <c r="A555" s="4">
         <v>553</v>
       </c>
-      <c r="B555" s="5" t="s">
+      <c r="B555" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C555" s="5" t="s">
+      <c r="C555" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="D555" s="5" t="s">
+      <c r="D555" s="1" t="s">
         <v>1450</v>
       </c>
       <c r="E555" s="4"/>
-      <c r="F555" s="5"/>
-      <c r="G555" s="5"/>
-      <c r="H555" s="5"/>
-      <c r="I555" s="5"/>
-      <c r="J555" s="5"/>
-      <c r="K555" s="5"/>
-      <c r="L555" s="6" t="str">
+      <c r="F555" s="1"/>
+      <c r="G555" s="1"/>
+      <c r="H555" s="1"/>
+      <c r="I555" s="1"/>
+      <c r="J555" s="1"/>
+      <c r="K555" s="1"/>
+      <c r="L555" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_FC80A17E97A84A409D08B98DAA9E6BFD",1)</f>
         <v>=DISPIMG("ID_FC80A17E97A84A409D08B98DAA9E6BFD",1)</v>
       </c>
     </row>
-    <row r="556" ht="38" customHeight="1" spans="1:12">
+    <row r="556" spans="1:12" ht="38" customHeight="1">
       <c r="A556" s="4">
         <v>554</v>
       </c>
-      <c r="B556" s="5" t="s">
+      <c r="B556" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C556" s="5" t="s">
+      <c r="C556" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="D556" s="5" t="s">
+      <c r="D556" s="1" t="s">
         <v>1450</v>
       </c>
       <c r="E556" s="4"/>
-      <c r="F556" s="5"/>
-      <c r="G556" s="5"/>
-      <c r="H556" s="5"/>
-      <c r="I556" s="5"/>
-      <c r="J556" s="5"/>
-      <c r="K556" s="5"/>
-      <c r="L556" s="6" t="str">
+      <c r="F556" s="1"/>
+      <c r="G556" s="1"/>
+      <c r="H556" s="1"/>
+      <c r="I556" s="1"/>
+      <c r="J556" s="1"/>
+      <c r="K556" s="1"/>
+      <c r="L556" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B4FD5D12C8BF4D97B018766EE22A85F7",1)</f>
         <v>=DISPIMG("ID_B4FD5D12C8BF4D97B018766EE22A85F7",1)</v>
       </c>
     </row>
-    <row r="557" ht="38" customHeight="1" spans="1:12">
+    <row r="557" spans="1:12" ht="38" customHeight="1">
       <c r="A557" s="4">
         <v>555</v>
       </c>
-      <c r="B557" s="5" t="s">
+      <c r="B557" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C557" s="5" t="s">
+      <c r="C557" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="D557" s="5" t="s">
+      <c r="D557" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E557" s="4"/>
-      <c r="F557" s="5"/>
-      <c r="G557" s="5"/>
-      <c r="H557" s="5"/>
-      <c r="I557" s="5"/>
-      <c r="J557" s="5"/>
-      <c r="K557" s="5"/>
-      <c r="L557" s="6" t="str">
+      <c r="F557" s="1"/>
+      <c r="G557" s="1"/>
+      <c r="H557" s="1"/>
+      <c r="I557" s="1"/>
+      <c r="J557" s="1"/>
+      <c r="K557" s="1"/>
+      <c r="L557" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_95B68F0F6BBF48DD9AD1AF6F1D7837FD",1)</f>
         <v>=DISPIMG("ID_95B68F0F6BBF48DD9AD1AF6F1D7837FD",1)</v>
       </c>
     </row>
-    <row r="558" ht="38" customHeight="1" spans="1:12">
+    <row r="558" spans="1:12" ht="38" customHeight="1">
       <c r="A558" s="4">
         <v>556</v>
       </c>
-      <c r="B558" s="5" t="s">
+      <c r="B558" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C558" s="5" t="s">
+      <c r="C558" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="D558" s="5" t="s">
+      <c r="D558" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E558" s="4"/>
-      <c r="F558" s="5"/>
-      <c r="G558" s="5"/>
-      <c r="H558" s="5"/>
-      <c r="I558" s="5"/>
-      <c r="J558" s="5"/>
-      <c r="K558" s="5"/>
-      <c r="L558" s="6" t="str">
+      <c r="F558" s="1"/>
+      <c r="G558" s="1"/>
+      <c r="H558" s="1"/>
+      <c r="I558" s="1"/>
+      <c r="J558" s="1"/>
+      <c r="K558" s="1"/>
+      <c r="L558" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_B07420BDE45A4C05A8E82E2EFEB36BFB",1)</f>
         <v>=DISPIMG("ID_B07420BDE45A4C05A8E82E2EFEB36BFB",1)</v>
       </c>
     </row>
-    <row r="559" ht="38" customHeight="1" spans="1:12">
+    <row r="559" spans="1:12" ht="38" customHeight="1">
       <c r="A559" s="4">
         <v>557</v>
       </c>
-      <c r="B559" s="5" t="s">
+      <c r="B559" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C559" s="5" t="s">
+      <c r="C559" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="D559" s="5" t="s">
+      <c r="D559" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E559" s="4"/>
-      <c r="F559" s="5" t="s">
+      <c r="F559" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G559" s="5"/>
-      <c r="H559" s="5"/>
-      <c r="I559" s="5"/>
-      <c r="J559" s="5"/>
-      <c r="K559" s="5"/>
-      <c r="L559" s="6" t="str">
+      <c r="G559" s="1"/>
+      <c r="H559" s="1"/>
+      <c r="I559" s="1"/>
+      <c r="J559" s="1"/>
+      <c r="K559" s="1"/>
+      <c r="L559" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D0E5EA151B6E41E1846206903249D618",1)</f>
         <v>=DISPIMG("ID_D0E5EA151B6E41E1846206903249D618",1)</v>
       </c>
     </row>
-    <row r="560" ht="38" customHeight="1" spans="1:12">
+    <row r="560" spans="1:12" ht="38" customHeight="1">
       <c r="A560" s="4">
         <v>558</v>
       </c>
-      <c r="B560" s="5" t="s">
+      <c r="B560" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="C560" s="5" t="s">
+      <c r="C560" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="D560" s="5" t="s">
+      <c r="D560" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E560" s="4">
         <v>433</v>
       </c>
-      <c r="F560" s="5" t="s">
+      <c r="F560" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G560" s="5"/>
-      <c r="H560" s="5"/>
-      <c r="I560" s="5"/>
-      <c r="J560" s="5"/>
-      <c r="K560" s="5"/>
-      <c r="L560" s="6" t="str">
+      <c r="G560" s="1"/>
+      <c r="H560" s="1"/>
+      <c r="I560" s="1"/>
+      <c r="J560" s="1"/>
+      <c r="K560" s="1"/>
+      <c r="L560" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_E9BCE1B188EE4465A114A1920B749310",1)</f>
         <v>=DISPIMG("ID_E9BCE1B188EE4465A114A1920B749310",1)</v>
       </c>
     </row>
-    <row r="561" ht="38" customHeight="1" spans="1:12">
+    <row r="561" spans="1:12" ht="38" customHeight="1">
       <c r="A561" s="4">
         <v>559</v>
       </c>
-      <c r="B561" s="5" t="s">
+      <c r="B561" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="C561" s="5" t="s">
+      <c r="C561" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="D561" s="5" t="s">
+      <c r="D561" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E561" s="4">
         <v>433</v>
       </c>
-      <c r="F561" s="5" t="s">
+      <c r="F561" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G561" s="5"/>
-      <c r="H561" s="5"/>
-      <c r="I561" s="5"/>
-      <c r="J561" s="5"/>
-      <c r="K561" s="5"/>
-      <c r="L561" s="6" t="str">
+      <c r="G561" s="1"/>
+      <c r="H561" s="1"/>
+      <c r="I561" s="1"/>
+      <c r="J561" s="1"/>
+      <c r="K561" s="1"/>
+      <c r="L561" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D91A75ACB8A74427A7D2412A7AA2E975",1)</f>
         <v>=DISPIMG("ID_D91A75ACB8A74427A7D2412A7AA2E975",1)</v>
       </c>
     </row>
-    <row r="562" ht="38" customHeight="1" spans="1:12">
+    <row r="562" spans="1:12" ht="38" customHeight="1">
       <c r="A562" s="4">
         <v>560</v>
       </c>
-      <c r="B562" s="5" t="s">
+      <c r="B562" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="C562" s="5" t="s">
+      <c r="C562" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="D562" s="5" t="s">
+      <c r="D562" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E562" s="4">
         <v>433</v>
       </c>
-      <c r="F562" s="5" t="s">
+      <c r="F562" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G562" s="5"/>
-      <c r="H562" s="5"/>
-      <c r="I562" s="5"/>
-      <c r="J562" s="5"/>
-      <c r="K562" s="5"/>
-      <c r="L562" s="6" t="s">
+      <c r="G562" s="1"/>
+      <c r="H562" s="1"/>
+      <c r="I562" s="1"/>
+      <c r="J562" s="1"/>
+      <c r="K562" s="1"/>
+      <c r="L562" s="1" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="563" ht="38" customHeight="1" spans="1:12">
+    <row r="563" spans="1:12" ht="38" customHeight="1">
       <c r="A563" s="4">
         <v>561</v>
       </c>
-      <c r="B563" s="5" t="s">
+      <c r="B563" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="C563" s="5" t="s">
+      <c r="C563" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="D563" s="5" t="s">
+      <c r="D563" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E563" s="4" t="s">
         <v>1463</v>
       </c>
-      <c r="F563" s="5" t="s">
+      <c r="F563" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G563" s="5"/>
-      <c r="H563" s="5"/>
-      <c r="I563" s="5"/>
-      <c r="J563" s="5"/>
-      <c r="K563" s="5"/>
-      <c r="L563" s="6" t="str">
+      <c r="G563" s="1"/>
+      <c r="H563" s="1"/>
+      <c r="I563" s="1"/>
+      <c r="J563" s="1"/>
+      <c r="K563" s="1"/>
+      <c r="L563" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D5C588A942EB4D3A9FE53FE84C99B056",1)</f>
         <v>=DISPIMG("ID_D5C588A942EB4D3A9FE53FE84C99B056",1)</v>
       </c>
     </row>
-    <row r="564" ht="38" customHeight="1" spans="1:12">
+    <row r="564" spans="1:12" ht="38" customHeight="1">
       <c r="A564" s="4">
         <v>562</v>
       </c>
-      <c r="B564" s="5" t="s">
+      <c r="B564" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="C564" s="5" t="s">
+      <c r="C564" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="D564" s="5" t="s">
+      <c r="D564" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E564" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="F564" s="5" t="s">
+      <c r="F564" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G564" s="5"/>
-      <c r="H564" s="5"/>
-      <c r="I564" s="5"/>
-      <c r="J564" s="5"/>
-      <c r="K564" s="5"/>
-      <c r="L564" s="6" t="str">
+      <c r="G564" s="1"/>
+      <c r="H564" s="1"/>
+      <c r="I564" s="1"/>
+      <c r="J564" s="1"/>
+      <c r="K564" s="1"/>
+      <c r="L564" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_2976606880D6488EB93B55817A91538D",1)</f>
         <v>=DISPIMG("ID_2976606880D6488EB93B55817A91538D",1)</v>
       </c>
     </row>
-    <row r="565" ht="38" customHeight="1" spans="1:12">
+    <row r="565" spans="1:12" ht="38" customHeight="1">
       <c r="A565" s="4">
         <v>563</v>
       </c>
-      <c r="B565" s="5" t="s">
+      <c r="B565" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="C565" s="5" t="s">
+      <c r="C565" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="D565" s="5" t="s">
+      <c r="D565" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E565" s="4" t="s">
         <v>1468</v>
       </c>
-      <c r="F565" s="5" t="s">
+      <c r="F565" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G565" s="5"/>
-      <c r="H565" s="5"/>
-      <c r="I565" s="5"/>
-      <c r="J565" s="5"/>
-      <c r="K565" s="5"/>
-      <c r="L565" s="6" t="str">
+      <c r="G565" s="1"/>
+      <c r="H565" s="1"/>
+      <c r="I565" s="1"/>
+      <c r="J565" s="1"/>
+      <c r="K565" s="1"/>
+      <c r="L565" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_EA164704ADE9435682E0DEBAB289EC4A",1)</f>
         <v>=DISPIMG("ID_EA164704ADE9435682E0DEBAB289EC4A",1)</v>
       </c>
     </row>
-    <row r="566" ht="38" customHeight="1" spans="1:12">
+    <row r="566" spans="1:12" ht="38" customHeight="1">
       <c r="A566" s="4">
         <v>564</v>
       </c>
-      <c r="B566" s="5" t="s">
+      <c r="B566" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="C566" s="5" t="s">
+      <c r="C566" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="D566" s="5" t="s">
+      <c r="D566" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E566" s="4" t="s">
         <v>1471</v>
       </c>
-      <c r="F566" s="5" t="s">
+      <c r="F566" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G566" s="5"/>
-      <c r="H566" s="5"/>
-      <c r="I566" s="5"/>
-      <c r="J566" s="5"/>
-      <c r="K566" s="5"/>
-      <c r="L566" s="6" t="str">
+      <c r="G566" s="1"/>
+      <c r="H566" s="1"/>
+      <c r="I566" s="1"/>
+      <c r="J566" s="1"/>
+      <c r="K566" s="1"/>
+      <c r="L566" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_65ADF02D959E4225820D056FF4F6096D",1)</f>
         <v>=DISPIMG("ID_65ADF02D959E4225820D056FF4F6096D",1)</v>
       </c>
     </row>
-    <row r="567" ht="38" customHeight="1" spans="1:12">
+    <row r="567" spans="1:12" ht="38" customHeight="1">
       <c r="A567" s="4">
         <v>565</v>
       </c>
-      <c r="B567" s="5" t="s">
+      <c r="B567" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="C567" s="5" t="s">
+      <c r="C567" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="D567" s="5" t="s">
+      <c r="D567" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E567" s="4"/>
-      <c r="F567" s="5"/>
-      <c r="G567" s="5"/>
-      <c r="H567" s="5"/>
-      <c r="I567" s="5"/>
-      <c r="J567" s="5"/>
-      <c r="K567" s="5"/>
-      <c r="L567" s="7" t="str">
+      <c r="F567" s="1"/>
+      <c r="G567" s="1"/>
+      <c r="H567" s="1"/>
+      <c r="I567" s="1"/>
+      <c r="J567" s="1"/>
+      <c r="K567" s="1"/>
+      <c r="L567" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_DF7DF9C46FE547CF92F83CD1B90CD130",1)</f>
         <v>=DISPIMG("ID_DF7DF9C46FE547CF92F83CD1B90CD130",1)</v>
       </c>
     </row>
-    <row r="568" ht="38" customHeight="1" spans="1:12">
+    <row r="568" spans="1:12" ht="38" customHeight="1">
       <c r="A568" s="4">
         <v>566</v>
       </c>
-      <c r="B568" s="5" t="s">
+      <c r="B568" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="C568" s="5" t="s">
+      <c r="C568" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="D568" s="5" t="s">
+      <c r="D568" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E568" s="4"/>
-      <c r="F568" s="5"/>
-      <c r="G568" s="5"/>
-      <c r="H568" s="5"/>
-      <c r="I568" s="5"/>
-      <c r="J568" s="5"/>
-      <c r="K568" s="5"/>
-      <c r="L568" s="7" t="str">
+      <c r="F568" s="1"/>
+      <c r="G568" s="1"/>
+      <c r="H568" s="1"/>
+      <c r="I568" s="1"/>
+      <c r="J568" s="1"/>
+      <c r="K568" s="1"/>
+      <c r="L568" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_67576DB2C8A54CD9B9E51371087BB802",1)</f>
         <v>=DISPIMG("ID_67576DB2C8A54CD9B9E51371087BB802",1)</v>
       </c>
     </row>
-    <row r="569" ht="38" customHeight="1" spans="1:12">
+    <row r="569" spans="1:12" ht="38" customHeight="1">
       <c r="A569" s="4">
         <v>567</v>
       </c>
-      <c r="B569" s="5" t="s">
+      <c r="B569" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="C569" s="5" t="s">
+      <c r="C569" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="D569" s="5" t="s">
+      <c r="D569" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E569" s="4"/>
-      <c r="F569" s="5"/>
-      <c r="G569" s="5"/>
-      <c r="H569" s="5"/>
-      <c r="I569" s="5"/>
-      <c r="J569" s="5"/>
-      <c r="K569" s="5"/>
-      <c r="L569" s="7" t="str">
+      <c r="F569" s="1"/>
+      <c r="G569" s="1"/>
+      <c r="H569" s="1"/>
+      <c r="I569" s="1"/>
+      <c r="J569" s="1"/>
+      <c r="K569" s="1"/>
+      <c r="L569" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_CFA10FA7BEEF49FE84B3479878F4B3BF",1)</f>
         <v>=DISPIMG("ID_CFA10FA7BEEF49FE84B3479878F4B3BF",1)</v>
       </c>
     </row>
-    <row r="570" ht="38" customHeight="1" spans="1:12">
+    <row r="570" spans="1:12" ht="38" customHeight="1">
       <c r="A570" s="4">
         <v>568</v>
       </c>
-      <c r="B570" s="5" t="s">
+      <c r="B570" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C570" s="5" t="s">
+      <c r="C570" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="D570" s="5" t="s">
+      <c r="D570" s="1" t="s">
         <v>589</v>
       </c>
       <c r="E570" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="F570" s="5"/>
-      <c r="G570" s="5"/>
-      <c r="H570" s="5"/>
-      <c r="I570" s="5"/>
-      <c r="J570" s="5"/>
-      <c r="K570" s="5"/>
-      <c r="L570" s="7" t="str">
+      <c r="F570" s="1"/>
+      <c r="G570" s="1"/>
+      <c r="H570" s="1"/>
+      <c r="I570" s="1"/>
+      <c r="J570" s="1"/>
+      <c r="K570" s="1"/>
+      <c r="L570" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_0AA38E35F0DE400FA2F1D4DD78E2B2B4",1)</f>
         <v>=DISPIMG("ID_0AA38E35F0DE400FA2F1D4DD78E2B2B4",1)</v>
       </c>
     </row>
-    <row r="571" ht="38" customHeight="1" spans="1:12">
+    <row r="571" spans="1:12" ht="38" customHeight="1">
       <c r="A571" s="4">
         <v>569</v>
       </c>
-      <c r="B571" s="5" t="s">
+      <c r="B571" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C571" s="5" t="s">
+      <c r="C571" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="D571" s="5" t="s">
+      <c r="D571" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="E571" s="4" t="s">
         <v>1481</v>
       </c>
-      <c r="F571" s="5"/>
-      <c r="G571" s="5"/>
-      <c r="H571" s="5"/>
-      <c r="I571" s="5"/>
-      <c r="J571" s="5"/>
-      <c r="K571" s="5"/>
-      <c r="L571" s="7" t="str">
+      <c r="F571" s="1"/>
+      <c r="G571" s="1"/>
+      <c r="H571" s="1"/>
+      <c r="I571" s="1"/>
+      <c r="J571" s="1"/>
+      <c r="K571" s="1"/>
+      <c r="L571" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_F7C64761E68E4B71AA49FD3AAE1E20EF",1)</f>
         <v>=DISPIMG("ID_F7C64761E68E4B71AA49FD3AAE1E20EF",1)</v>
       </c>
     </row>
-    <row r="572" ht="38" customHeight="1" spans="1:12">
+    <row r="572" spans="1:12" ht="38" customHeight="1">
       <c r="A572" s="4">
         <v>570</v>
       </c>
-      <c r="B572" s="5" t="s">
+      <c r="B572" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C572" s="5" t="s">
+      <c r="C572" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="D572" s="5" t="s">
+      <c r="D572" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="E572" s="4" t="s">
         <v>1483</v>
       </c>
-      <c r="F572" s="5"/>
-      <c r="G572" s="5"/>
-      <c r="H572" s="5"/>
-      <c r="I572" s="5"/>
-      <c r="J572" s="5"/>
-      <c r="K572" s="5"/>
-      <c r="L572" s="7" t="str">
+      <c r="F572" s="1"/>
+      <c r="G572" s="1"/>
+      <c r="H572" s="1"/>
+      <c r="I572" s="1"/>
+      <c r="J572" s="1"/>
+      <c r="K572" s="1"/>
+      <c r="L572" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_959DEC91805E4802AAE8CE595BAF01B3",1)</f>
         <v>=DISPIMG("ID_959DEC91805E4802AAE8CE595BAF01B3",1)</v>
       </c>
     </row>
-    <row r="573" ht="38" customHeight="1" spans="1:12">
+    <row r="573" spans="1:12" ht="38" customHeight="1">
       <c r="A573" s="4">
         <v>571</v>
       </c>
-      <c r="B573" s="5" t="s">
+      <c r="B573" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C573" s="5" t="s">
+      <c r="C573" s="1" t="s">
         <v>1484</v>
       </c>
-      <c r="D573" s="5" t="s">
+      <c r="D573" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="E573" s="4" t="s">
         <v>1485</v>
       </c>
-      <c r="F573" s="5"/>
-      <c r="G573" s="5"/>
-      <c r="H573" s="5"/>
-      <c r="I573" s="5"/>
-      <c r="J573" s="5"/>
-      <c r="K573" s="5"/>
-      <c r="L573" s="7" t="str">
+      <c r="F573" s="1"/>
+      <c r="G573" s="1"/>
+      <c r="H573" s="1"/>
+      <c r="I573" s="1"/>
+      <c r="J573" s="1"/>
+      <c r="K573" s="1"/>
+      <c r="L573" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_FD33E4311D5D475597EB7C558D0AB4FA",1)</f>
         <v>=DISPIMG("ID_FD33E4311D5D475597EB7C558D0AB4FA",1)</v>
       </c>
     </row>
-    <row r="574" ht="38" customHeight="1" spans="1:12">
+    <row r="574" spans="1:12" ht="38" customHeight="1">
       <c r="A574" s="4">
         <v>572</v>
       </c>
-      <c r="B574" s="5" t="s">
+      <c r="B574" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C574" s="5" t="s">
+      <c r="C574" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="D574" s="5" t="s">
+      <c r="D574" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="E574" s="4" t="s">
         <v>1487</v>
       </c>
-      <c r="F574" s="5"/>
-      <c r="G574" s="5"/>
-      <c r="H574" s="5"/>
-      <c r="I574" s="5"/>
-      <c r="J574" s="5"/>
-      <c r="K574" s="5"/>
-      <c r="L574" s="7" t="str">
+      <c r="F574" s="1"/>
+      <c r="G574" s="1"/>
+      <c r="H574" s="1"/>
+      <c r="I574" s="1"/>
+      <c r="J574" s="1"/>
+      <c r="K574" s="1"/>
+      <c r="L574" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_30D5B2A0FA6C48299D364CAF99720D14",1)</f>
         <v>=DISPIMG("ID_30D5B2A0FA6C48299D364CAF99720D14",1)</v>
       </c>
     </row>
-    <row r="575" ht="38" customHeight="1" spans="1:12">
+    <row r="575" spans="1:12" ht="38" customHeight="1">
       <c r="A575" s="4">
         <v>573</v>
       </c>
-      <c r="B575" s="5" t="s">
+      <c r="B575" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C575" s="5" t="s">
+      <c r="C575" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="D575" s="5" t="s">
+      <c r="D575" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="E575" s="4" t="s">
         <v>1489</v>
       </c>
-      <c r="F575" s="5"/>
-      <c r="G575" s="5"/>
-      <c r="H575" s="5"/>
-      <c r="I575" s="5"/>
-      <c r="J575" s="5"/>
-      <c r="K575" s="5"/>
-      <c r="L575" s="7" t="str">
+      <c r="F575" s="1"/>
+      <c r="G575" s="1"/>
+      <c r="H575" s="1"/>
+      <c r="I575" s="1"/>
+      <c r="J575" s="1"/>
+      <c r="K575" s="1"/>
+      <c r="L575" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_88A9949FDDEC4E169AE3FBB6C807C2CE",1)</f>
         <v>=DISPIMG("ID_88A9949FDDEC4E169AE3FBB6C807C2CE",1)</v>
       </c>
     </row>
-    <row r="576" ht="38" customHeight="1" spans="1:12">
+    <row r="576" spans="1:12" ht="38" customHeight="1">
       <c r="A576" s="4">
         <v>574</v>
       </c>
-      <c r="B576" s="5" t="s">
+      <c r="B576" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="C576" s="5" t="s">
+      <c r="C576" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="D576" s="5" t="s">
+      <c r="D576" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E576" s="4" t="s">
         <v>1492</v>
       </c>
-      <c r="F576" s="5" t="s">
+      <c r="F576" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G576" s="5"/>
-      <c r="H576" s="5"/>
-      <c r="I576" s="5"/>
-      <c r="J576" s="5"/>
-      <c r="K576" s="5"/>
-      <c r="L576" s="7" t="str">
+      <c r="G576" s="1"/>
+      <c r="H576" s="1"/>
+      <c r="I576" s="1"/>
+      <c r="J576" s="1"/>
+      <c r="K576" s="1"/>
+      <c r="L576" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D8A0E2846E9A4AE6B49AC04DAA6B68C8",1)</f>
         <v>=DISPIMG("ID_D8A0E2846E9A4AE6B49AC04DAA6B68C8",1)</v>
       </c>
     </row>
-    <row r="577" ht="38" customHeight="1" spans="1:12">
+    <row r="577" spans="1:12" ht="38" customHeight="1">
       <c r="A577" s="4">
         <v>575</v>
       </c>
-      <c r="B577" s="5" t="s">
+      <c r="B577" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="C577" s="5" t="s">
+      <c r="C577" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="D577" s="5" t="s">
+      <c r="D577" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E577" s="4"/>
-      <c r="F577" s="5" t="s">
+      <c r="F577" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="G577" s="5"/>
-      <c r="H577" s="5"/>
-      <c r="I577" s="5"/>
-      <c r="J577" s="5"/>
-      <c r="K577" s="5"/>
-      <c r="L577" s="7" t="str">
+      <c r="G577" s="1"/>
+      <c r="H577" s="1"/>
+      <c r="I577" s="1"/>
+      <c r="J577" s="1"/>
+      <c r="K577" s="1"/>
+      <c r="L577" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_A721BEEF63F1430DA3EB37908EE2323A",1)</f>
         <v>=DISPIMG("ID_A721BEEF63F1430DA3EB37908EE2323A",1)</v>
       </c>
     </row>
-    <row r="578" ht="38" customHeight="1" spans="1:12">
+    <row r="578" spans="1:12" ht="38" customHeight="1">
       <c r="A578" s="4">
         <v>576</v>
       </c>
-      <c r="B578" s="5" t="s">
+      <c r="B578" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C578" s="5" t="s">
+      <c r="C578" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="D578" s="5" t="s">
+      <c r="D578" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E578" s="4"/>
-      <c r="F578" s="5" t="s">
+      <c r="F578" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="G578" s="5"/>
-      <c r="H578" s="5"/>
-      <c r="I578" s="5"/>
-      <c r="J578" s="5"/>
-      <c r="K578" s="5"/>
-      <c r="L578" s="7" t="str">
+      <c r="G578" s="1"/>
+      <c r="H578" s="1"/>
+      <c r="I578" s="1"/>
+      <c r="J578" s="1"/>
+      <c r="K578" s="1"/>
+      <c r="L578" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_0A80DBD4F7B1478DAEA6235E41CDFA7E",1)</f>
         <v>=DISPIMG("ID_0A80DBD4F7B1478DAEA6235E41CDFA7E",1)</v>
       </c>
     </row>
-    <row r="579" ht="38" customHeight="1" spans="1:12">
+    <row r="579" spans="1:12" ht="38" customHeight="1">
       <c r="A579" s="4">
         <v>577</v>
       </c>
-      <c r="B579" s="5" t="s">
+      <c r="B579" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C579" s="5" t="s">
+      <c r="C579" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="D579" s="5" t="s">
+      <c r="D579" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E579" s="4"/>
-      <c r="F579" s="5" t="s">
+      <c r="F579" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="G579" s="5"/>
-      <c r="H579" s="5"/>
-      <c r="I579" s="5"/>
-      <c r="J579" s="5"/>
-      <c r="K579" s="5"/>
-      <c r="L579" s="7" t="str">
+      <c r="G579" s="1"/>
+      <c r="H579" s="1"/>
+      <c r="I579" s="1"/>
+      <c r="J579" s="1"/>
+      <c r="K579" s="1"/>
+      <c r="L579" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_D06BDCDBCB16440E9A702F85B224EF8E",1)</f>
         <v>=DISPIMG("ID_D06BDCDBCB16440E9A702F85B224EF8E",1)</v>
       </c>
     </row>
-    <row r="580" ht="38" customHeight="1" spans="1:12">
+    <row r="580" spans="1:12" ht="38" customHeight="1">
       <c r="A580" s="4">
         <v>578</v>
       </c>
-      <c r="B580" s="5" t="s">
+      <c r="B580" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C580" s="5" t="s">
+      <c r="C580" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="D580" s="5" t="s">
+      <c r="D580" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E580" s="4"/>
-      <c r="F580" s="5" t="s">
+      <c r="F580" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="G580" s="5"/>
-      <c r="H580" s="5"/>
-      <c r="I580" s="5"/>
-      <c r="J580" s="5"/>
-      <c r="K580" s="5"/>
-      <c r="L580" s="7" t="str">
+      <c r="G580" s="1"/>
+      <c r="H580" s="1"/>
+      <c r="I580" s="1"/>
+      <c r="J580" s="1"/>
+      <c r="K580" s="1"/>
+      <c r="L580" s="1" t="str">
         <f>_xlfn.DISPIMG("ID_29516A3EB44945AC9CC982E063DEAAFB",1)</f>
         <v>=DISPIMG("ID_29516A3EB44945AC9CC982E063DEAAFB",1)</v>
       </c>
     </row>
-    <row r="581" ht="38" customHeight="1"/>
-    <row r="582" ht="38" customHeight="1"/>
-    <row r="583" ht="38" customHeight="1"/>
-    <row r="584" ht="38" customHeight="1"/>
-    <row r="585" ht="38" customHeight="1"/>
-    <row r="586" ht="38" customHeight="1"/>
-    <row r="587" ht="38" customHeight="1"/>
-    <row r="588" ht="38" customHeight="1"/>
-    <row r="589" ht="38" customHeight="1"/>
-    <row r="590" ht="38" customHeight="1"/>
-    <row r="591" ht="38" customHeight="1"/>
-    <row r="592" ht="38" customHeight="1"/>
+    <row r="581" spans="1:12" ht="38" customHeight="1"/>
+    <row r="582" spans="1:12" ht="38" customHeight="1"/>
+    <row r="583" spans="1:12" ht="38" customHeight="1"/>
+    <row r="584" spans="1:12" ht="38" customHeight="1"/>
+    <row r="585" spans="1:12" ht="38" customHeight="1"/>
+    <row r="586" spans="1:12" ht="38" customHeight="1"/>
+    <row r="587" spans="1:12" ht="38" customHeight="1"/>
+    <row r="588" spans="1:12" ht="38" customHeight="1"/>
+    <row r="589" spans="1:12" ht="38" customHeight="1"/>
+    <row r="590" spans="1:12" ht="38" customHeight="1"/>
+    <row r="591" spans="1:12" ht="38" customHeight="1"/>
+    <row r="592" spans="1:12" ht="38" customHeight="1"/>
     <row r="593" ht="38" customHeight="1"/>
     <row r="594" ht="38" customHeight="1"/>
     <row r="595" ht="38" customHeight="1"/>
@@ -22939,13 +22322,10 @@
     <row r="715" ht="38" customHeight="1"/>
     <row r="716" ht="38" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:L716" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>